--- a/recursos/comercial/INDUCCION_COMERCIAL/contratacion comercial/TABLERO_ALIANZAS.xlsx
+++ b/recursos/comercial/INDUCCION_COMERCIAL/contratacion comercial/TABLERO_ALIANZAS.xlsx
@@ -11,9 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TABLERO" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMPRESAS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIVIDAD_DIARIA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METAS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIQUIDACION" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRIMERA_SEMANA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLAN_SEMANAL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METAS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIQUIDACION" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRIMERA_SEMANA" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,10 +23,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="MMMM YYYY"/>
+    <numFmt numFmtId="166" formatCode="DD/MM/YYYY HH:MM"/>
+    <numFmt numFmtId="167" formatCode="HH:MM"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="MMMM YYYY"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -97,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +120,14 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -507,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -590,47 +602,55 @@
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2. ACTIVIDAD_DIARIA: al cierre de cada día, una fila: contactos nuevos con decisor, reuniones, activaciones, firmas, ventas firmadas, plan de mañana y bloqueos. Es lo que se presenta en la reunión diaria de 15 minutos.</t>
+          <t>2. ACTIVIDAD_DIARIA: al cierre de cada día, antes de las 6:00 p. m., una fila: contactos y reuniones con empresas, personas contactadas, citas, inscritos pagados, caja, lo más importante, mañana hago y bloqueos. Es el reporte diario; gerencia lo lee en Drive.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>3. TABLERO: se calcula solo. Muestra el mes contra los mínimos, el semáforo y las fechas de decisión. Gerencia lo revisa a diario.</t>
+          <t>2b. PLAN_SEMANAL: el lunes antes de las 8:30 a. m. se llena la semana (franjas, lugar, qué) y se comparte con coordinación. Es el registro de la jornada: 42 horas.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>4. LIQUIDACION: contaduría o gerencia registra lo RECAUDADO en el mes por cada empresa y cada estudiante atribuido; la comisión se calcula sola. Se liquida el día 5 de cada mes y se paga con la nómina.</t>
+          <t>3. TABLERO: se calcula solo. Muestra el mes contra los mínimos, el semáforo y las fechas de decisión. Gerencia lo revisa a diario.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>5. METAS: tabla pactada en el anexo del contrato (no se cambia sin otrosí).</t>
+          <t>4. LIQUIDACION: contaduría o gerencia registra lo RECAUDADO en el mes por cada empresa y cada estudiante atribuido; la comisión se calcula sola. Se liquida el día 5 de cada mes y se paga con la nómina.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>6. PRIMERA_SEMANA: plan de arranque y benchmarking de la competencia.</t>
+          <t>5. METAS: tabla pactada en el anexo del contrato (no se cambia sin otrosí).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>6. PRIMERA_SEMANA: plan de arranque y benchmarking de la competencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>Definiciones: CONTACTO = habló con quien puede firmar (no recepción). REUNIÓN = presentación de 20+ min con quien decide. FIRMA = convenio firmado u orden de plan empresa firmada CON inicial pagada. ACTIVACIÓN = charla, postulación, feria o jornada en una alianza firmada. VENTA FIRMADA = valor total del contrato con inicial pagada (contado o cuotas).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A13:F13"/>
@@ -7249,7 +7269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I301"/>
+  <dimension ref="A1:O301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7258,9 +7278,14 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -7296,2119 +7321,2444 @@
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
+          <t>Personas contactadas (referidos, conocidos, afiliados)</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Citas con personas hechas</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Inscritos pagados hoy (personas)</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Caja recibida hoy ($)</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
           <t>Lo más importante de hoy</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>Plan de mañana (empresas / reuniones)</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>Bloqueos / ayuda que necesito</t>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Mañana hago (empresas / reuniones / citas)</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>Bloqueos / lo que necesito de gerencia</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Se llena al cierre de cada día, antes de las 6:00 p. m., una fila por día (también los días sin resultados: se escribe 0). Gerencia la lee en Drive sin pedirla.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="n"/>
       <c r="F2" s="12" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="12" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
       <c r="F3" s="12" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="12" t="n"/>
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
+      <c r="M3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
       <c r="F4" s="12" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
+      <c r="M4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
       <c r="F5" s="12" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
       <c r="F6" s="12" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
       <c r="F7" s="12" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
       <c r="F8" s="12" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
       <c r="F9" s="12" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
       <c r="F10" s="12" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
       <c r="F11" s="12" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
       <c r="F12" s="12" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
       <c r="F13" s="12" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
       <c r="F14" s="12" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
       <c r="F15" s="12" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="F16" s="12" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
       <c r="F17" s="12" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
       <c r="F18" s="12" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
       <c r="F19" s="12" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
       <c r="F20" s="12" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
       <c r="F21" s="12" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
       <c r="F22" s="12" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
       <c r="F23" s="12" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
       <c r="F24" s="12" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="7" t="n"/>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
       <c r="F25" s="12" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
       <c r="F26" s="12" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
       <c r="F27" s="12" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
       <c r="F28" s="12" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
       <c r="F29" s="12" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="7" t="n"/>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
       <c r="F30" s="12" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="7" t="n"/>
+      <c r="L30" s="7" t="n"/>
+      <c r="M30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
       <c r="F31" s="12" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
       <c r="F32" s="12" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
       <c r="F33" s="12" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
       <c r="F34" s="12" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
       <c r="F35" s="12" t="n"/>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
       <c r="F36" s="12" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
       <c r="F37" s="12" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
       <c r="F38" s="12" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
       <c r="F39" s="12" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n"/>
-      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="7" t="n"/>
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
       <c r="F40" s="12" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="7" t="n"/>
+      <c r="J40" s="12" t="n"/>
+      <c r="K40" s="7" t="n"/>
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
       <c r="F41" s="12" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="7" t="n"/>
+      <c r="J41" s="12" t="n"/>
+      <c r="K41" s="7" t="n"/>
+      <c r="L41" s="7" t="n"/>
+      <c r="M41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
       <c r="F42" s="12" t="n"/>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="7" t="n"/>
-      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="7" t="n"/>
+      <c r="L42" s="7" t="n"/>
+      <c r="M42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
       <c r="F43" s="12" t="n"/>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n"/>
-      <c r="I43" s="7" t="n"/>
+      <c r="J43" s="12" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
       <c r="F44" s="12" t="n"/>
-      <c r="G44" s="7" t="n"/>
-      <c r="H44" s="7" t="n"/>
-      <c r="I44" s="7" t="n"/>
+      <c r="J44" s="12" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
       <c r="F45" s="12" t="n"/>
-      <c r="G45" s="7" t="n"/>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="7" t="n"/>
+      <c r="J45" s="12" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
       <c r="F46" s="12" t="n"/>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="7" t="n"/>
+      <c r="J46" s="12" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
       <c r="F47" s="12" t="n"/>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="12" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
       <c r="F48" s="12" t="n"/>
-      <c r="G48" s="7" t="n"/>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="7" t="n"/>
+      <c r="J48" s="12" t="n"/>
+      <c r="K48" s="7" t="n"/>
+      <c r="L48" s="7" t="n"/>
+      <c r="M48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
       <c r="F49" s="12" t="n"/>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="7" t="n"/>
+      <c r="J49" s="12" t="n"/>
+      <c r="K49" s="7" t="n"/>
+      <c r="L49" s="7" t="n"/>
+      <c r="M49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
       <c r="F50" s="12" t="n"/>
-      <c r="G50" s="7" t="n"/>
-      <c r="H50" s="7" t="n"/>
-      <c r="I50" s="7" t="n"/>
+      <c r="J50" s="12" t="n"/>
+      <c r="K50" s="7" t="n"/>
+      <c r="L50" s="7" t="n"/>
+      <c r="M50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
       <c r="F51" s="12" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
+      <c r="J51" s="12" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
       <c r="F52" s="12" t="n"/>
-      <c r="G52" s="7" t="n"/>
-      <c r="H52" s="7" t="n"/>
-      <c r="I52" s="7" t="n"/>
+      <c r="J52" s="12" t="n"/>
+      <c r="K52" s="7" t="n"/>
+      <c r="L52" s="7" t="n"/>
+      <c r="M52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
       <c r="F53" s="12" t="n"/>
-      <c r="G53" s="7" t="n"/>
-      <c r="H53" s="7" t="n"/>
-      <c r="I53" s="7" t="n"/>
+      <c r="J53" s="12" t="n"/>
+      <c r="K53" s="7" t="n"/>
+      <c r="L53" s="7" t="n"/>
+      <c r="M53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
       <c r="F54" s="12" t="n"/>
-      <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="n"/>
-      <c r="I54" s="7" t="n"/>
+      <c r="J54" s="12" t="n"/>
+      <c r="K54" s="7" t="n"/>
+      <c r="L54" s="7" t="n"/>
+      <c r="M54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
       <c r="F55" s="12" t="n"/>
-      <c r="G55" s="7" t="n"/>
-      <c r="H55" s="7" t="n"/>
-      <c r="I55" s="7" t="n"/>
+      <c r="J55" s="12" t="n"/>
+      <c r="K55" s="7" t="n"/>
+      <c r="L55" s="7" t="n"/>
+      <c r="M55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
       <c r="F56" s="12" t="n"/>
-      <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
-      <c r="I56" s="7" t="n"/>
+      <c r="J56" s="12" t="n"/>
+      <c r="K56" s="7" t="n"/>
+      <c r="L56" s="7" t="n"/>
+      <c r="M56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
       <c r="F57" s="12" t="n"/>
-      <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="n"/>
-      <c r="I57" s="7" t="n"/>
+      <c r="J57" s="12" t="n"/>
+      <c r="K57" s="7" t="n"/>
+      <c r="L57" s="7" t="n"/>
+      <c r="M57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
       <c r="F58" s="12" t="n"/>
-      <c r="G58" s="7" t="n"/>
-      <c r="H58" s="7" t="n"/>
-      <c r="I58" s="7" t="n"/>
+      <c r="J58" s="12" t="n"/>
+      <c r="K58" s="7" t="n"/>
+      <c r="L58" s="7" t="n"/>
+      <c r="M58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
       <c r="F59" s="12" t="n"/>
-      <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="n"/>
-      <c r="I59" s="7" t="n"/>
+      <c r="J59" s="12" t="n"/>
+      <c r="K59" s="7" t="n"/>
+      <c r="L59" s="7" t="n"/>
+      <c r="M59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
       <c r="F60" s="12" t="n"/>
-      <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="n"/>
-      <c r="I60" s="7" t="n"/>
+      <c r="J60" s="12" t="n"/>
+      <c r="K60" s="7" t="n"/>
+      <c r="L60" s="7" t="n"/>
+      <c r="M60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
       <c r="F61" s="12" t="n"/>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
+      <c r="J61" s="12" t="n"/>
+      <c r="K61" s="7" t="n"/>
+      <c r="L61" s="7" t="n"/>
+      <c r="M61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n"/>
       <c r="F62" s="12" t="n"/>
-      <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="7" t="n"/>
+      <c r="J62" s="12" t="n"/>
+      <c r="K62" s="7" t="n"/>
+      <c r="L62" s="7" t="n"/>
+      <c r="M62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
       <c r="F63" s="12" t="n"/>
-      <c r="G63" s="7" t="n"/>
-      <c r="H63" s="7" t="n"/>
-      <c r="I63" s="7" t="n"/>
+      <c r="J63" s="12" t="n"/>
+      <c r="K63" s="7" t="n"/>
+      <c r="L63" s="7" t="n"/>
+      <c r="M63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
       <c r="F64" s="12" t="n"/>
-      <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="7" t="n"/>
+      <c r="J64" s="12" t="n"/>
+      <c r="K64" s="7" t="n"/>
+      <c r="L64" s="7" t="n"/>
+      <c r="M64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n"/>
       <c r="F65" s="12" t="n"/>
-      <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="n"/>
-      <c r="I65" s="7" t="n"/>
+      <c r="J65" s="12" t="n"/>
+      <c r="K65" s="7" t="n"/>
+      <c r="L65" s="7" t="n"/>
+      <c r="M65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>
       <c r="F66" s="12" t="n"/>
-      <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
-      <c r="I66" s="7" t="n"/>
+      <c r="J66" s="12" t="n"/>
+      <c r="K66" s="7" t="n"/>
+      <c r="L66" s="7" t="n"/>
+      <c r="M66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n"/>
       <c r="F67" s="12" t="n"/>
-      <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
-      <c r="I67" s="7" t="n"/>
+      <c r="J67" s="12" t="n"/>
+      <c r="K67" s="7" t="n"/>
+      <c r="L67" s="7" t="n"/>
+      <c r="M67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
       <c r="F68" s="12" t="n"/>
-      <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
-      <c r="I68" s="7" t="n"/>
+      <c r="J68" s="12" t="n"/>
+      <c r="K68" s="7" t="n"/>
+      <c r="L68" s="7" t="n"/>
+      <c r="M68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n"/>
       <c r="F69" s="12" t="n"/>
-      <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
-      <c r="I69" s="7" t="n"/>
+      <c r="J69" s="12" t="n"/>
+      <c r="K69" s="7" t="n"/>
+      <c r="L69" s="7" t="n"/>
+      <c r="M69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n"/>
       <c r="F70" s="12" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
-      <c r="I70" s="7" t="n"/>
+      <c r="J70" s="12" t="n"/>
+      <c r="K70" s="7" t="n"/>
+      <c r="L70" s="7" t="n"/>
+      <c r="M70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n"/>
       <c r="F71" s="12" t="n"/>
-      <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
-      <c r="I71" s="7" t="n"/>
+      <c r="J71" s="12" t="n"/>
+      <c r="K71" s="7" t="n"/>
+      <c r="L71" s="7" t="n"/>
+      <c r="M71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
       <c r="F72" s="12" t="n"/>
-      <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="n"/>
-      <c r="I72" s="7" t="n"/>
+      <c r="J72" s="12" t="n"/>
+      <c r="K72" s="7" t="n"/>
+      <c r="L72" s="7" t="n"/>
+      <c r="M72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n"/>
       <c r="F73" s="12" t="n"/>
-      <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="n"/>
-      <c r="I73" s="7" t="n"/>
+      <c r="J73" s="12" t="n"/>
+      <c r="K73" s="7" t="n"/>
+      <c r="L73" s="7" t="n"/>
+      <c r="M73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n"/>
       <c r="F74" s="12" t="n"/>
-      <c r="G74" s="7" t="n"/>
-      <c r="H74" s="7" t="n"/>
-      <c r="I74" s="7" t="n"/>
+      <c r="J74" s="12" t="n"/>
+      <c r="K74" s="7" t="n"/>
+      <c r="L74" s="7" t="n"/>
+      <c r="M74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n"/>
       <c r="F75" s="12" t="n"/>
-      <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="n"/>
-      <c r="I75" s="7" t="n"/>
+      <c r="J75" s="12" t="n"/>
+      <c r="K75" s="7" t="n"/>
+      <c r="L75" s="7" t="n"/>
+      <c r="M75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
       <c r="F76" s="12" t="n"/>
-      <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
+      <c r="J76" s="12" t="n"/>
+      <c r="K76" s="7" t="n"/>
+      <c r="L76" s="7" t="n"/>
+      <c r="M76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n"/>
       <c r="F77" s="12" t="n"/>
-      <c r="G77" s="7" t="n"/>
-      <c r="H77" s="7" t="n"/>
-      <c r="I77" s="7" t="n"/>
+      <c r="J77" s="12" t="n"/>
+      <c r="K77" s="7" t="n"/>
+      <c r="L77" s="7" t="n"/>
+      <c r="M77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n"/>
       <c r="F78" s="12" t="n"/>
-      <c r="G78" s="7" t="n"/>
-      <c r="H78" s="7" t="n"/>
-      <c r="I78" s="7" t="n"/>
+      <c r="J78" s="12" t="n"/>
+      <c r="K78" s="7" t="n"/>
+      <c r="L78" s="7" t="n"/>
+      <c r="M78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n"/>
       <c r="F79" s="12" t="n"/>
-      <c r="G79" s="7" t="n"/>
-      <c r="H79" s="7" t="n"/>
-      <c r="I79" s="7" t="n"/>
+      <c r="J79" s="12" t="n"/>
+      <c r="K79" s="7" t="n"/>
+      <c r="L79" s="7" t="n"/>
+      <c r="M79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
       <c r="F80" s="12" t="n"/>
-      <c r="G80" s="7" t="n"/>
-      <c r="H80" s="7" t="n"/>
-      <c r="I80" s="7" t="n"/>
+      <c r="J80" s="12" t="n"/>
+      <c r="K80" s="7" t="n"/>
+      <c r="L80" s="7" t="n"/>
+      <c r="M80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n"/>
       <c r="F81" s="12" t="n"/>
-      <c r="G81" s="7" t="n"/>
-      <c r="H81" s="7" t="n"/>
-      <c r="I81" s="7" t="n"/>
+      <c r="J81" s="12" t="n"/>
+      <c r="K81" s="7" t="n"/>
+      <c r="L81" s="7" t="n"/>
+      <c r="M81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n"/>
       <c r="F82" s="12" t="n"/>
-      <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="n"/>
-      <c r="I82" s="7" t="n"/>
+      <c r="J82" s="12" t="n"/>
+      <c r="K82" s="7" t="n"/>
+      <c r="L82" s="7" t="n"/>
+      <c r="M82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n"/>
       <c r="F83" s="12" t="n"/>
-      <c r="G83" s="7" t="n"/>
-      <c r="H83" s="7" t="n"/>
-      <c r="I83" s="7" t="n"/>
+      <c r="J83" s="12" t="n"/>
+      <c r="K83" s="7" t="n"/>
+      <c r="L83" s="7" t="n"/>
+      <c r="M83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
       <c r="F84" s="12" t="n"/>
-      <c r="G84" s="7" t="n"/>
-      <c r="H84" s="7" t="n"/>
-      <c r="I84" s="7" t="n"/>
+      <c r="J84" s="12" t="n"/>
+      <c r="K84" s="7" t="n"/>
+      <c r="L84" s="7" t="n"/>
+      <c r="M84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n"/>
       <c r="F85" s="12" t="n"/>
-      <c r="G85" s="7" t="n"/>
-      <c r="H85" s="7" t="n"/>
-      <c r="I85" s="7" t="n"/>
+      <c r="J85" s="12" t="n"/>
+      <c r="K85" s="7" t="n"/>
+      <c r="L85" s="7" t="n"/>
+      <c r="M85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n"/>
       <c r="F86" s="12" t="n"/>
-      <c r="G86" s="7" t="n"/>
-      <c r="H86" s="7" t="n"/>
-      <c r="I86" s="7" t="n"/>
+      <c r="J86" s="12" t="n"/>
+      <c r="K86" s="7" t="n"/>
+      <c r="L86" s="7" t="n"/>
+      <c r="M86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n"/>
       <c r="F87" s="12" t="n"/>
-      <c r="G87" s="7" t="n"/>
-      <c r="H87" s="7" t="n"/>
-      <c r="I87" s="7" t="n"/>
+      <c r="J87" s="12" t="n"/>
+      <c r="K87" s="7" t="n"/>
+      <c r="L87" s="7" t="n"/>
+      <c r="M87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n"/>
       <c r="F88" s="12" t="n"/>
-      <c r="G88" s="7" t="n"/>
-      <c r="H88" s="7" t="n"/>
-      <c r="I88" s="7" t="n"/>
+      <c r="J88" s="12" t="n"/>
+      <c r="K88" s="7" t="n"/>
+      <c r="L88" s="7" t="n"/>
+      <c r="M88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n"/>
       <c r="F89" s="12" t="n"/>
-      <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
-      <c r="I89" s="7" t="n"/>
+      <c r="J89" s="12" t="n"/>
+      <c r="K89" s="7" t="n"/>
+      <c r="L89" s="7" t="n"/>
+      <c r="M89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n"/>
       <c r="F90" s="12" t="n"/>
-      <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="n"/>
-      <c r="I90" s="7" t="n"/>
+      <c r="J90" s="12" t="n"/>
+      <c r="K90" s="7" t="n"/>
+      <c r="L90" s="7" t="n"/>
+      <c r="M90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n"/>
       <c r="F91" s="12" t="n"/>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="n"/>
-      <c r="I91" s="7" t="n"/>
+      <c r="J91" s="12" t="n"/>
+      <c r="K91" s="7" t="n"/>
+      <c r="L91" s="7" t="n"/>
+      <c r="M91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n"/>
       <c r="F92" s="12" t="n"/>
-      <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="n"/>
-      <c r="I92" s="7" t="n"/>
+      <c r="J92" s="12" t="n"/>
+      <c r="K92" s="7" t="n"/>
+      <c r="L92" s="7" t="n"/>
+      <c r="M92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
       <c r="F93" s="12" t="n"/>
-      <c r="G93" s="7" t="n"/>
-      <c r="H93" s="7" t="n"/>
-      <c r="I93" s="7" t="n"/>
+      <c r="J93" s="12" t="n"/>
+      <c r="K93" s="7" t="n"/>
+      <c r="L93" s="7" t="n"/>
+      <c r="M93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n"/>
       <c r="F94" s="12" t="n"/>
-      <c r="G94" s="7" t="n"/>
-      <c r="H94" s="7" t="n"/>
-      <c r="I94" s="7" t="n"/>
+      <c r="J94" s="12" t="n"/>
+      <c r="K94" s="7" t="n"/>
+      <c r="L94" s="7" t="n"/>
+      <c r="M94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n"/>
       <c r="F95" s="12" t="n"/>
-      <c r="G95" s="7" t="n"/>
-      <c r="H95" s="7" t="n"/>
-      <c r="I95" s="7" t="n"/>
+      <c r="J95" s="12" t="n"/>
+      <c r="K95" s="7" t="n"/>
+      <c r="L95" s="7" t="n"/>
+      <c r="M95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n"/>
       <c r="F96" s="12" t="n"/>
-      <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
-      <c r="I96" s="7" t="n"/>
+      <c r="J96" s="12" t="n"/>
+      <c r="K96" s="7" t="n"/>
+      <c r="L96" s="7" t="n"/>
+      <c r="M96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n"/>
       <c r="F97" s="12" t="n"/>
-      <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
-      <c r="I97" s="7" t="n"/>
+      <c r="J97" s="12" t="n"/>
+      <c r="K97" s="7" t="n"/>
+      <c r="L97" s="7" t="n"/>
+      <c r="M97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n"/>
       <c r="F98" s="12" t="n"/>
-      <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
-      <c r="I98" s="7" t="n"/>
+      <c r="J98" s="12" t="n"/>
+      <c r="K98" s="7" t="n"/>
+      <c r="L98" s="7" t="n"/>
+      <c r="M98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n"/>
       <c r="F99" s="12" t="n"/>
-      <c r="G99" s="7" t="n"/>
-      <c r="H99" s="7" t="n"/>
-      <c r="I99" s="7" t="n"/>
+      <c r="J99" s="12" t="n"/>
+      <c r="K99" s="7" t="n"/>
+      <c r="L99" s="7" t="n"/>
+      <c r="M99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n"/>
       <c r="F100" s="12" t="n"/>
-      <c r="G100" s="7" t="n"/>
-      <c r="H100" s="7" t="n"/>
-      <c r="I100" s="7" t="n"/>
+      <c r="J100" s="12" t="n"/>
+      <c r="K100" s="7" t="n"/>
+      <c r="L100" s="7" t="n"/>
+      <c r="M100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n"/>
       <c r="F101" s="12" t="n"/>
-      <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="n"/>
-      <c r="I101" s="7" t="n"/>
+      <c r="J101" s="12" t="n"/>
+      <c r="K101" s="7" t="n"/>
+      <c r="L101" s="7" t="n"/>
+      <c r="M101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n"/>
       <c r="F102" s="12" t="n"/>
-      <c r="G102" s="7" t="n"/>
-      <c r="H102" s="7" t="n"/>
-      <c r="I102" s="7" t="n"/>
+      <c r="J102" s="12" t="n"/>
+      <c r="K102" s="7" t="n"/>
+      <c r="L102" s="7" t="n"/>
+      <c r="M102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n"/>
       <c r="F103" s="12" t="n"/>
-      <c r="G103" s="7" t="n"/>
-      <c r="H103" s="7" t="n"/>
-      <c r="I103" s="7" t="n"/>
+      <c r="J103" s="12" t="n"/>
+      <c r="K103" s="7" t="n"/>
+      <c r="L103" s="7" t="n"/>
+      <c r="M103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n"/>
       <c r="F104" s="12" t="n"/>
-      <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="n"/>
-      <c r="I104" s="7" t="n"/>
+      <c r="J104" s="12" t="n"/>
+      <c r="K104" s="7" t="n"/>
+      <c r="L104" s="7" t="n"/>
+      <c r="M104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n"/>
       <c r="F105" s="12" t="n"/>
-      <c r="G105" s="7" t="n"/>
-      <c r="H105" s="7" t="n"/>
-      <c r="I105" s="7" t="n"/>
+      <c r="J105" s="12" t="n"/>
+      <c r="K105" s="7" t="n"/>
+      <c r="L105" s="7" t="n"/>
+      <c r="M105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n"/>
       <c r="F106" s="12" t="n"/>
-      <c r="G106" s="7" t="n"/>
-      <c r="H106" s="7" t="n"/>
-      <c r="I106" s="7" t="n"/>
+      <c r="J106" s="12" t="n"/>
+      <c r="K106" s="7" t="n"/>
+      <c r="L106" s="7" t="n"/>
+      <c r="M106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n"/>
       <c r="F107" s="12" t="n"/>
-      <c r="G107" s="7" t="n"/>
-      <c r="H107" s="7" t="n"/>
-      <c r="I107" s="7" t="n"/>
+      <c r="J107" s="12" t="n"/>
+      <c r="K107" s="7" t="n"/>
+      <c r="L107" s="7" t="n"/>
+      <c r="M107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n"/>
       <c r="F108" s="12" t="n"/>
-      <c r="G108" s="7" t="n"/>
-      <c r="H108" s="7" t="n"/>
-      <c r="I108" s="7" t="n"/>
+      <c r="J108" s="12" t="n"/>
+      <c r="K108" s="7" t="n"/>
+      <c r="L108" s="7" t="n"/>
+      <c r="M108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n"/>
       <c r="F109" s="12" t="n"/>
-      <c r="G109" s="7" t="n"/>
-      <c r="H109" s="7" t="n"/>
-      <c r="I109" s="7" t="n"/>
+      <c r="J109" s="12" t="n"/>
+      <c r="K109" s="7" t="n"/>
+      <c r="L109" s="7" t="n"/>
+      <c r="M109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n"/>
       <c r="F110" s="12" t="n"/>
-      <c r="G110" s="7" t="n"/>
-      <c r="H110" s="7" t="n"/>
-      <c r="I110" s="7" t="n"/>
+      <c r="J110" s="12" t="n"/>
+      <c r="K110" s="7" t="n"/>
+      <c r="L110" s="7" t="n"/>
+      <c r="M110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n"/>
       <c r="F111" s="12" t="n"/>
-      <c r="G111" s="7" t="n"/>
-      <c r="H111" s="7" t="n"/>
-      <c r="I111" s="7" t="n"/>
+      <c r="J111" s="12" t="n"/>
+      <c r="K111" s="7" t="n"/>
+      <c r="L111" s="7" t="n"/>
+      <c r="M111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n"/>
       <c r="F112" s="12" t="n"/>
-      <c r="G112" s="7" t="n"/>
-      <c r="H112" s="7" t="n"/>
-      <c r="I112" s="7" t="n"/>
+      <c r="J112" s="12" t="n"/>
+      <c r="K112" s="7" t="n"/>
+      <c r="L112" s="7" t="n"/>
+      <c r="M112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n"/>
       <c r="F113" s="12" t="n"/>
-      <c r="G113" s="7" t="n"/>
-      <c r="H113" s="7" t="n"/>
-      <c r="I113" s="7" t="n"/>
+      <c r="J113" s="12" t="n"/>
+      <c r="K113" s="7" t="n"/>
+      <c r="L113" s="7" t="n"/>
+      <c r="M113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n"/>
       <c r="F114" s="12" t="n"/>
-      <c r="G114" s="7" t="n"/>
-      <c r="H114" s="7" t="n"/>
-      <c r="I114" s="7" t="n"/>
+      <c r="J114" s="12" t="n"/>
+      <c r="K114" s="7" t="n"/>
+      <c r="L114" s="7" t="n"/>
+      <c r="M114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n"/>
       <c r="F115" s="12" t="n"/>
-      <c r="G115" s="7" t="n"/>
-      <c r="H115" s="7" t="n"/>
-      <c r="I115" s="7" t="n"/>
+      <c r="J115" s="12" t="n"/>
+      <c r="K115" s="7" t="n"/>
+      <c r="L115" s="7" t="n"/>
+      <c r="M115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n"/>
       <c r="F116" s="12" t="n"/>
-      <c r="G116" s="7" t="n"/>
-      <c r="H116" s="7" t="n"/>
-      <c r="I116" s="7" t="n"/>
+      <c r="J116" s="12" t="n"/>
+      <c r="K116" s="7" t="n"/>
+      <c r="L116" s="7" t="n"/>
+      <c r="M116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n"/>
       <c r="F117" s="12" t="n"/>
-      <c r="G117" s="7" t="n"/>
-      <c r="H117" s="7" t="n"/>
-      <c r="I117" s="7" t="n"/>
+      <c r="J117" s="12" t="n"/>
+      <c r="K117" s="7" t="n"/>
+      <c r="L117" s="7" t="n"/>
+      <c r="M117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n"/>
       <c r="F118" s="12" t="n"/>
-      <c r="G118" s="7" t="n"/>
-      <c r="H118" s="7" t="n"/>
-      <c r="I118" s="7" t="n"/>
+      <c r="J118" s="12" t="n"/>
+      <c r="K118" s="7" t="n"/>
+      <c r="L118" s="7" t="n"/>
+      <c r="M118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n"/>
       <c r="F119" s="12" t="n"/>
-      <c r="G119" s="7" t="n"/>
-      <c r="H119" s="7" t="n"/>
-      <c r="I119" s="7" t="n"/>
+      <c r="J119" s="12" t="n"/>
+      <c r="K119" s="7" t="n"/>
+      <c r="L119" s="7" t="n"/>
+      <c r="M119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n"/>
       <c r="F120" s="12" t="n"/>
-      <c r="G120" s="7" t="n"/>
-      <c r="H120" s="7" t="n"/>
-      <c r="I120" s="7" t="n"/>
+      <c r="J120" s="12" t="n"/>
+      <c r="K120" s="7" t="n"/>
+      <c r="L120" s="7" t="n"/>
+      <c r="M120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n"/>
       <c r="F121" s="12" t="n"/>
-      <c r="G121" s="7" t="n"/>
-      <c r="H121" s="7" t="n"/>
-      <c r="I121" s="7" t="n"/>
+      <c r="J121" s="12" t="n"/>
+      <c r="K121" s="7" t="n"/>
+      <c r="L121" s="7" t="n"/>
+      <c r="M121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n"/>
       <c r="F122" s="12" t="n"/>
-      <c r="G122" s="7" t="n"/>
-      <c r="H122" s="7" t="n"/>
-      <c r="I122" s="7" t="n"/>
+      <c r="J122" s="12" t="n"/>
+      <c r="K122" s="7" t="n"/>
+      <c r="L122" s="7" t="n"/>
+      <c r="M122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n"/>
       <c r="F123" s="12" t="n"/>
-      <c r="G123" s="7" t="n"/>
-      <c r="H123" s="7" t="n"/>
-      <c r="I123" s="7" t="n"/>
+      <c r="J123" s="12" t="n"/>
+      <c r="K123" s="7" t="n"/>
+      <c r="L123" s="7" t="n"/>
+      <c r="M123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="n"/>
       <c r="F124" s="12" t="n"/>
-      <c r="G124" s="7" t="n"/>
-      <c r="H124" s="7" t="n"/>
-      <c r="I124" s="7" t="n"/>
+      <c r="J124" s="12" t="n"/>
+      <c r="K124" s="7" t="n"/>
+      <c r="L124" s="7" t="n"/>
+      <c r="M124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n"/>
       <c r="F125" s="12" t="n"/>
-      <c r="G125" s="7" t="n"/>
-      <c r="H125" s="7" t="n"/>
-      <c r="I125" s="7" t="n"/>
+      <c r="J125" s="12" t="n"/>
+      <c r="K125" s="7" t="n"/>
+      <c r="L125" s="7" t="n"/>
+      <c r="M125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="n"/>
       <c r="F126" s="12" t="n"/>
-      <c r="G126" s="7" t="n"/>
-      <c r="H126" s="7" t="n"/>
-      <c r="I126" s="7" t="n"/>
+      <c r="J126" s="12" t="n"/>
+      <c r="K126" s="7" t="n"/>
+      <c r="L126" s="7" t="n"/>
+      <c r="M126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n"/>
       <c r="F127" s="12" t="n"/>
-      <c r="G127" s="7" t="n"/>
-      <c r="H127" s="7" t="n"/>
-      <c r="I127" s="7" t="n"/>
+      <c r="J127" s="12" t="n"/>
+      <c r="K127" s="7" t="n"/>
+      <c r="L127" s="7" t="n"/>
+      <c r="M127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="n"/>
       <c r="F128" s="12" t="n"/>
-      <c r="G128" s="7" t="n"/>
-      <c r="H128" s="7" t="n"/>
-      <c r="I128" s="7" t="n"/>
+      <c r="J128" s="12" t="n"/>
+      <c r="K128" s="7" t="n"/>
+      <c r="L128" s="7" t="n"/>
+      <c r="M128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="n"/>
       <c r="F129" s="12" t="n"/>
-      <c r="G129" s="7" t="n"/>
-      <c r="H129" s="7" t="n"/>
-      <c r="I129" s="7" t="n"/>
+      <c r="J129" s="12" t="n"/>
+      <c r="K129" s="7" t="n"/>
+      <c r="L129" s="7" t="n"/>
+      <c r="M129" s="7" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n"/>
       <c r="F130" s="12" t="n"/>
-      <c r="G130" s="7" t="n"/>
-      <c r="H130" s="7" t="n"/>
-      <c r="I130" s="7" t="n"/>
+      <c r="J130" s="12" t="n"/>
+      <c r="K130" s="7" t="n"/>
+      <c r="L130" s="7" t="n"/>
+      <c r="M130" s="7" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="n"/>
       <c r="F131" s="12" t="n"/>
-      <c r="G131" s="7" t="n"/>
-      <c r="H131" s="7" t="n"/>
-      <c r="I131" s="7" t="n"/>
+      <c r="J131" s="12" t="n"/>
+      <c r="K131" s="7" t="n"/>
+      <c r="L131" s="7" t="n"/>
+      <c r="M131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n"/>
       <c r="F132" s="12" t="n"/>
-      <c r="G132" s="7" t="n"/>
-      <c r="H132" s="7" t="n"/>
-      <c r="I132" s="7" t="n"/>
+      <c r="J132" s="12" t="n"/>
+      <c r="K132" s="7" t="n"/>
+      <c r="L132" s="7" t="n"/>
+      <c r="M132" s="7" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n"/>
       <c r="F133" s="12" t="n"/>
-      <c r="G133" s="7" t="n"/>
-      <c r="H133" s="7" t="n"/>
-      <c r="I133" s="7" t="n"/>
+      <c r="J133" s="12" t="n"/>
+      <c r="K133" s="7" t="n"/>
+      <c r="L133" s="7" t="n"/>
+      <c r="M133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="n"/>
       <c r="F134" s="12" t="n"/>
-      <c r="G134" s="7" t="n"/>
-      <c r="H134" s="7" t="n"/>
-      <c r="I134" s="7" t="n"/>
+      <c r="J134" s="12" t="n"/>
+      <c r="K134" s="7" t="n"/>
+      <c r="L134" s="7" t="n"/>
+      <c r="M134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n"/>
       <c r="F135" s="12" t="n"/>
-      <c r="G135" s="7" t="n"/>
-      <c r="H135" s="7" t="n"/>
-      <c r="I135" s="7" t="n"/>
+      <c r="J135" s="12" t="n"/>
+      <c r="K135" s="7" t="n"/>
+      <c r="L135" s="7" t="n"/>
+      <c r="M135" s="7" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="n"/>
       <c r="F136" s="12" t="n"/>
-      <c r="G136" s="7" t="n"/>
-      <c r="H136" s="7" t="n"/>
-      <c r="I136" s="7" t="n"/>
+      <c r="J136" s="12" t="n"/>
+      <c r="K136" s="7" t="n"/>
+      <c r="L136" s="7" t="n"/>
+      <c r="M136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n"/>
       <c r="F137" s="12" t="n"/>
-      <c r="G137" s="7" t="n"/>
-      <c r="H137" s="7" t="n"/>
-      <c r="I137" s="7" t="n"/>
+      <c r="J137" s="12" t="n"/>
+      <c r="K137" s="7" t="n"/>
+      <c r="L137" s="7" t="n"/>
+      <c r="M137" s="7" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="n"/>
       <c r="F138" s="12" t="n"/>
-      <c r="G138" s="7" t="n"/>
-      <c r="H138" s="7" t="n"/>
-      <c r="I138" s="7" t="n"/>
+      <c r="J138" s="12" t="n"/>
+      <c r="K138" s="7" t="n"/>
+      <c r="L138" s="7" t="n"/>
+      <c r="M138" s="7" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n"/>
       <c r="F139" s="12" t="n"/>
-      <c r="G139" s="7" t="n"/>
-      <c r="H139" s="7" t="n"/>
-      <c r="I139" s="7" t="n"/>
+      <c r="J139" s="12" t="n"/>
+      <c r="K139" s="7" t="n"/>
+      <c r="L139" s="7" t="n"/>
+      <c r="M139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="n"/>
       <c r="F140" s="12" t="n"/>
-      <c r="G140" s="7" t="n"/>
-      <c r="H140" s="7" t="n"/>
-      <c r="I140" s="7" t="n"/>
+      <c r="J140" s="12" t="n"/>
+      <c r="K140" s="7" t="n"/>
+      <c r="L140" s="7" t="n"/>
+      <c r="M140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="n"/>
       <c r="F141" s="12" t="n"/>
-      <c r="G141" s="7" t="n"/>
-      <c r="H141" s="7" t="n"/>
-      <c r="I141" s="7" t="n"/>
+      <c r="J141" s="12" t="n"/>
+      <c r="K141" s="7" t="n"/>
+      <c r="L141" s="7" t="n"/>
+      <c r="M141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="n"/>
       <c r="F142" s="12" t="n"/>
-      <c r="G142" s="7" t="n"/>
-      <c r="H142" s="7" t="n"/>
-      <c r="I142" s="7" t="n"/>
+      <c r="J142" s="12" t="n"/>
+      <c r="K142" s="7" t="n"/>
+      <c r="L142" s="7" t="n"/>
+      <c r="M142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="n"/>
       <c r="F143" s="12" t="n"/>
-      <c r="G143" s="7" t="n"/>
-      <c r="H143" s="7" t="n"/>
-      <c r="I143" s="7" t="n"/>
+      <c r="J143" s="12" t="n"/>
+      <c r="K143" s="7" t="n"/>
+      <c r="L143" s="7" t="n"/>
+      <c r="M143" s="7" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="n"/>
       <c r="F144" s="12" t="n"/>
-      <c r="G144" s="7" t="n"/>
-      <c r="H144" s="7" t="n"/>
-      <c r="I144" s="7" t="n"/>
+      <c r="J144" s="12" t="n"/>
+      <c r="K144" s="7" t="n"/>
+      <c r="L144" s="7" t="n"/>
+      <c r="M144" s="7" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n"/>
       <c r="F145" s="12" t="n"/>
-      <c r="G145" s="7" t="n"/>
-      <c r="H145" s="7" t="n"/>
-      <c r="I145" s="7" t="n"/>
+      <c r="J145" s="12" t="n"/>
+      <c r="K145" s="7" t="n"/>
+      <c r="L145" s="7" t="n"/>
+      <c r="M145" s="7" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="n"/>
       <c r="F146" s="12" t="n"/>
-      <c r="G146" s="7" t="n"/>
-      <c r="H146" s="7" t="n"/>
-      <c r="I146" s="7" t="n"/>
+      <c r="J146" s="12" t="n"/>
+      <c r="K146" s="7" t="n"/>
+      <c r="L146" s="7" t="n"/>
+      <c r="M146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="n"/>
       <c r="F147" s="12" t="n"/>
-      <c r="G147" s="7" t="n"/>
-      <c r="H147" s="7" t="n"/>
-      <c r="I147" s="7" t="n"/>
+      <c r="J147" s="12" t="n"/>
+      <c r="K147" s="7" t="n"/>
+      <c r="L147" s="7" t="n"/>
+      <c r="M147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="n"/>
       <c r="F148" s="12" t="n"/>
-      <c r="G148" s="7" t="n"/>
-      <c r="H148" s="7" t="n"/>
-      <c r="I148" s="7" t="n"/>
+      <c r="J148" s="12" t="n"/>
+      <c r="K148" s="7" t="n"/>
+      <c r="L148" s="7" t="n"/>
+      <c r="M148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="n"/>
       <c r="F149" s="12" t="n"/>
-      <c r="G149" s="7" t="n"/>
-      <c r="H149" s="7" t="n"/>
-      <c r="I149" s="7" t="n"/>
+      <c r="J149" s="12" t="n"/>
+      <c r="K149" s="7" t="n"/>
+      <c r="L149" s="7" t="n"/>
+      <c r="M149" s="7" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="n"/>
       <c r="F150" s="12" t="n"/>
-      <c r="G150" s="7" t="n"/>
-      <c r="H150" s="7" t="n"/>
-      <c r="I150" s="7" t="n"/>
+      <c r="J150" s="12" t="n"/>
+      <c r="K150" s="7" t="n"/>
+      <c r="L150" s="7" t="n"/>
+      <c r="M150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="n"/>
       <c r="F151" s="12" t="n"/>
-      <c r="G151" s="7" t="n"/>
-      <c r="H151" s="7" t="n"/>
-      <c r="I151" s="7" t="n"/>
+      <c r="J151" s="12" t="n"/>
+      <c r="K151" s="7" t="n"/>
+      <c r="L151" s="7" t="n"/>
+      <c r="M151" s="7" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="n"/>
       <c r="F152" s="12" t="n"/>
-      <c r="G152" s="7" t="n"/>
-      <c r="H152" s="7" t="n"/>
-      <c r="I152" s="7" t="n"/>
+      <c r="J152" s="12" t="n"/>
+      <c r="K152" s="7" t="n"/>
+      <c r="L152" s="7" t="n"/>
+      <c r="M152" s="7" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="n"/>
       <c r="F153" s="12" t="n"/>
-      <c r="G153" s="7" t="n"/>
-      <c r="H153" s="7" t="n"/>
-      <c r="I153" s="7" t="n"/>
+      <c r="J153" s="12" t="n"/>
+      <c r="K153" s="7" t="n"/>
+      <c r="L153" s="7" t="n"/>
+      <c r="M153" s="7" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="n"/>
       <c r="F154" s="12" t="n"/>
-      <c r="G154" s="7" t="n"/>
-      <c r="H154" s="7" t="n"/>
-      <c r="I154" s="7" t="n"/>
+      <c r="J154" s="12" t="n"/>
+      <c r="K154" s="7" t="n"/>
+      <c r="L154" s="7" t="n"/>
+      <c r="M154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="n"/>
       <c r="F155" s="12" t="n"/>
-      <c r="G155" s="7" t="n"/>
-      <c r="H155" s="7" t="n"/>
-      <c r="I155" s="7" t="n"/>
+      <c r="J155" s="12" t="n"/>
+      <c r="K155" s="7" t="n"/>
+      <c r="L155" s="7" t="n"/>
+      <c r="M155" s="7" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="n"/>
       <c r="F156" s="12" t="n"/>
-      <c r="G156" s="7" t="n"/>
-      <c r="H156" s="7" t="n"/>
-      <c r="I156" s="7" t="n"/>
+      <c r="J156" s="12" t="n"/>
+      <c r="K156" s="7" t="n"/>
+      <c r="L156" s="7" t="n"/>
+      <c r="M156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="n"/>
       <c r="F157" s="12" t="n"/>
-      <c r="G157" s="7" t="n"/>
-      <c r="H157" s="7" t="n"/>
-      <c r="I157" s="7" t="n"/>
+      <c r="J157" s="12" t="n"/>
+      <c r="K157" s="7" t="n"/>
+      <c r="L157" s="7" t="n"/>
+      <c r="M157" s="7" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="n"/>
       <c r="F158" s="12" t="n"/>
-      <c r="G158" s="7" t="n"/>
-      <c r="H158" s="7" t="n"/>
-      <c r="I158" s="7" t="n"/>
+      <c r="J158" s="12" t="n"/>
+      <c r="K158" s="7" t="n"/>
+      <c r="L158" s="7" t="n"/>
+      <c r="M158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="n"/>
       <c r="F159" s="12" t="n"/>
-      <c r="G159" s="7" t="n"/>
-      <c r="H159" s="7" t="n"/>
-      <c r="I159" s="7" t="n"/>
+      <c r="J159" s="12" t="n"/>
+      <c r="K159" s="7" t="n"/>
+      <c r="L159" s="7" t="n"/>
+      <c r="M159" s="7" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n"/>
       <c r="F160" s="12" t="n"/>
-      <c r="G160" s="7" t="n"/>
-      <c r="H160" s="7" t="n"/>
-      <c r="I160" s="7" t="n"/>
+      <c r="J160" s="12" t="n"/>
+      <c r="K160" s="7" t="n"/>
+      <c r="L160" s="7" t="n"/>
+      <c r="M160" s="7" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n"/>
       <c r="F161" s="12" t="n"/>
-      <c r="G161" s="7" t="n"/>
-      <c r="H161" s="7" t="n"/>
-      <c r="I161" s="7" t="n"/>
+      <c r="J161" s="12" t="n"/>
+      <c r="K161" s="7" t="n"/>
+      <c r="L161" s="7" t="n"/>
+      <c r="M161" s="7" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="n"/>
       <c r="F162" s="12" t="n"/>
-      <c r="G162" s="7" t="n"/>
-      <c r="H162" s="7" t="n"/>
-      <c r="I162" s="7" t="n"/>
+      <c r="J162" s="12" t="n"/>
+      <c r="K162" s="7" t="n"/>
+      <c r="L162" s="7" t="n"/>
+      <c r="M162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="n"/>
       <c r="F163" s="12" t="n"/>
-      <c r="G163" s="7" t="n"/>
-      <c r="H163" s="7" t="n"/>
-      <c r="I163" s="7" t="n"/>
+      <c r="J163" s="12" t="n"/>
+      <c r="K163" s="7" t="n"/>
+      <c r="L163" s="7" t="n"/>
+      <c r="M163" s="7" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="n"/>
       <c r="F164" s="12" t="n"/>
-      <c r="G164" s="7" t="n"/>
-      <c r="H164" s="7" t="n"/>
-      <c r="I164" s="7" t="n"/>
+      <c r="J164" s="12" t="n"/>
+      <c r="K164" s="7" t="n"/>
+      <c r="L164" s="7" t="n"/>
+      <c r="M164" s="7" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="n"/>
       <c r="F165" s="12" t="n"/>
-      <c r="G165" s="7" t="n"/>
-      <c r="H165" s="7" t="n"/>
-      <c r="I165" s="7" t="n"/>
+      <c r="J165" s="12" t="n"/>
+      <c r="K165" s="7" t="n"/>
+      <c r="L165" s="7" t="n"/>
+      <c r="M165" s="7" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="n"/>
       <c r="F166" s="12" t="n"/>
-      <c r="G166" s="7" t="n"/>
-      <c r="H166" s="7" t="n"/>
-      <c r="I166" s="7" t="n"/>
+      <c r="J166" s="12" t="n"/>
+      <c r="K166" s="7" t="n"/>
+      <c r="L166" s="7" t="n"/>
+      <c r="M166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="n"/>
       <c r="F167" s="12" t="n"/>
-      <c r="G167" s="7" t="n"/>
-      <c r="H167" s="7" t="n"/>
-      <c r="I167" s="7" t="n"/>
+      <c r="J167" s="12" t="n"/>
+      <c r="K167" s="7" t="n"/>
+      <c r="L167" s="7" t="n"/>
+      <c r="M167" s="7" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="n"/>
       <c r="F168" s="12" t="n"/>
-      <c r="G168" s="7" t="n"/>
-      <c r="H168" s="7" t="n"/>
-      <c r="I168" s="7" t="n"/>
+      <c r="J168" s="12" t="n"/>
+      <c r="K168" s="7" t="n"/>
+      <c r="L168" s="7" t="n"/>
+      <c r="M168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="n"/>
       <c r="F169" s="12" t="n"/>
-      <c r="G169" s="7" t="n"/>
-      <c r="H169" s="7" t="n"/>
-      <c r="I169" s="7" t="n"/>
+      <c r="J169" s="12" t="n"/>
+      <c r="K169" s="7" t="n"/>
+      <c r="L169" s="7" t="n"/>
+      <c r="M169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="n"/>
       <c r="F170" s="12" t="n"/>
-      <c r="G170" s="7" t="n"/>
-      <c r="H170" s="7" t="n"/>
-      <c r="I170" s="7" t="n"/>
+      <c r="J170" s="12" t="n"/>
+      <c r="K170" s="7" t="n"/>
+      <c r="L170" s="7" t="n"/>
+      <c r="M170" s="7" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="n"/>
       <c r="F171" s="12" t="n"/>
-      <c r="G171" s="7" t="n"/>
-      <c r="H171" s="7" t="n"/>
-      <c r="I171" s="7" t="n"/>
+      <c r="J171" s="12" t="n"/>
+      <c r="K171" s="7" t="n"/>
+      <c r="L171" s="7" t="n"/>
+      <c r="M171" s="7" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="n"/>
       <c r="F172" s="12" t="n"/>
-      <c r="G172" s="7" t="n"/>
-      <c r="H172" s="7" t="n"/>
-      <c r="I172" s="7" t="n"/>
+      <c r="J172" s="12" t="n"/>
+      <c r="K172" s="7" t="n"/>
+      <c r="L172" s="7" t="n"/>
+      <c r="M172" s="7" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="n"/>
       <c r="F173" s="12" t="n"/>
-      <c r="G173" s="7" t="n"/>
-      <c r="H173" s="7" t="n"/>
-      <c r="I173" s="7" t="n"/>
+      <c r="J173" s="12" t="n"/>
+      <c r="K173" s="7" t="n"/>
+      <c r="L173" s="7" t="n"/>
+      <c r="M173" s="7" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="n"/>
       <c r="F174" s="12" t="n"/>
-      <c r="G174" s="7" t="n"/>
-      <c r="H174" s="7" t="n"/>
-      <c r="I174" s="7" t="n"/>
+      <c r="J174" s="12" t="n"/>
+      <c r="K174" s="7" t="n"/>
+      <c r="L174" s="7" t="n"/>
+      <c r="M174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="n"/>
       <c r="F175" s="12" t="n"/>
-      <c r="G175" s="7" t="n"/>
-      <c r="H175" s="7" t="n"/>
-      <c r="I175" s="7" t="n"/>
+      <c r="J175" s="12" t="n"/>
+      <c r="K175" s="7" t="n"/>
+      <c r="L175" s="7" t="n"/>
+      <c r="M175" s="7" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="n"/>
       <c r="F176" s="12" t="n"/>
-      <c r="G176" s="7" t="n"/>
-      <c r="H176" s="7" t="n"/>
-      <c r="I176" s="7" t="n"/>
+      <c r="J176" s="12" t="n"/>
+      <c r="K176" s="7" t="n"/>
+      <c r="L176" s="7" t="n"/>
+      <c r="M176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="n"/>
       <c r="F177" s="12" t="n"/>
-      <c r="G177" s="7" t="n"/>
-      <c r="H177" s="7" t="n"/>
-      <c r="I177" s="7" t="n"/>
+      <c r="J177" s="12" t="n"/>
+      <c r="K177" s="7" t="n"/>
+      <c r="L177" s="7" t="n"/>
+      <c r="M177" s="7" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="n"/>
       <c r="F178" s="12" t="n"/>
-      <c r="G178" s="7" t="n"/>
-      <c r="H178" s="7" t="n"/>
-      <c r="I178" s="7" t="n"/>
+      <c r="J178" s="12" t="n"/>
+      <c r="K178" s="7" t="n"/>
+      <c r="L178" s="7" t="n"/>
+      <c r="M178" s="7" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="n"/>
       <c r="F179" s="12" t="n"/>
-      <c r="G179" s="7" t="n"/>
-      <c r="H179" s="7" t="n"/>
-      <c r="I179" s="7" t="n"/>
+      <c r="J179" s="12" t="n"/>
+      <c r="K179" s="7" t="n"/>
+      <c r="L179" s="7" t="n"/>
+      <c r="M179" s="7" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="n"/>
       <c r="F180" s="12" t="n"/>
-      <c r="G180" s="7" t="n"/>
-      <c r="H180" s="7" t="n"/>
-      <c r="I180" s="7" t="n"/>
+      <c r="J180" s="12" t="n"/>
+      <c r="K180" s="7" t="n"/>
+      <c r="L180" s="7" t="n"/>
+      <c r="M180" s="7" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="n"/>
       <c r="F181" s="12" t="n"/>
-      <c r="G181" s="7" t="n"/>
-      <c r="H181" s="7" t="n"/>
-      <c r="I181" s="7" t="n"/>
+      <c r="J181" s="12" t="n"/>
+      <c r="K181" s="7" t="n"/>
+      <c r="L181" s="7" t="n"/>
+      <c r="M181" s="7" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="n"/>
       <c r="F182" s="12" t="n"/>
-      <c r="G182" s="7" t="n"/>
-      <c r="H182" s="7" t="n"/>
-      <c r="I182" s="7" t="n"/>
+      <c r="J182" s="12" t="n"/>
+      <c r="K182" s="7" t="n"/>
+      <c r="L182" s="7" t="n"/>
+      <c r="M182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="n"/>
       <c r="F183" s="12" t="n"/>
-      <c r="G183" s="7" t="n"/>
-      <c r="H183" s="7" t="n"/>
-      <c r="I183" s="7" t="n"/>
+      <c r="J183" s="12" t="n"/>
+      <c r="K183" s="7" t="n"/>
+      <c r="L183" s="7" t="n"/>
+      <c r="M183" s="7" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="n"/>
       <c r="F184" s="12" t="n"/>
-      <c r="G184" s="7" t="n"/>
-      <c r="H184" s="7" t="n"/>
-      <c r="I184" s="7" t="n"/>
+      <c r="J184" s="12" t="n"/>
+      <c r="K184" s="7" t="n"/>
+      <c r="L184" s="7" t="n"/>
+      <c r="M184" s="7" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="n"/>
       <c r="F185" s="12" t="n"/>
-      <c r="G185" s="7" t="n"/>
-      <c r="H185" s="7" t="n"/>
-      <c r="I185" s="7" t="n"/>
+      <c r="J185" s="12" t="n"/>
+      <c r="K185" s="7" t="n"/>
+      <c r="L185" s="7" t="n"/>
+      <c r="M185" s="7" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="n"/>
       <c r="F186" s="12" t="n"/>
-      <c r="G186" s="7" t="n"/>
-      <c r="H186" s="7" t="n"/>
-      <c r="I186" s="7" t="n"/>
+      <c r="J186" s="12" t="n"/>
+      <c r="K186" s="7" t="n"/>
+      <c r="L186" s="7" t="n"/>
+      <c r="M186" s="7" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="n"/>
       <c r="F187" s="12" t="n"/>
-      <c r="G187" s="7" t="n"/>
-      <c r="H187" s="7" t="n"/>
-      <c r="I187" s="7" t="n"/>
+      <c r="J187" s="12" t="n"/>
+      <c r="K187" s="7" t="n"/>
+      <c r="L187" s="7" t="n"/>
+      <c r="M187" s="7" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="n"/>
       <c r="F188" s="12" t="n"/>
-      <c r="G188" s="7" t="n"/>
-      <c r="H188" s="7" t="n"/>
-      <c r="I188" s="7" t="n"/>
+      <c r="J188" s="12" t="n"/>
+      <c r="K188" s="7" t="n"/>
+      <c r="L188" s="7" t="n"/>
+      <c r="M188" s="7" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="n"/>
       <c r="F189" s="12" t="n"/>
-      <c r="G189" s="7" t="n"/>
-      <c r="H189" s="7" t="n"/>
-      <c r="I189" s="7" t="n"/>
+      <c r="J189" s="12" t="n"/>
+      <c r="K189" s="7" t="n"/>
+      <c r="L189" s="7" t="n"/>
+      <c r="M189" s="7" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="n"/>
       <c r="F190" s="12" t="n"/>
-      <c r="G190" s="7" t="n"/>
-      <c r="H190" s="7" t="n"/>
-      <c r="I190" s="7" t="n"/>
+      <c r="J190" s="12" t="n"/>
+      <c r="K190" s="7" t="n"/>
+      <c r="L190" s="7" t="n"/>
+      <c r="M190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="n"/>
       <c r="F191" s="12" t="n"/>
-      <c r="G191" s="7" t="n"/>
-      <c r="H191" s="7" t="n"/>
-      <c r="I191" s="7" t="n"/>
+      <c r="J191" s="12" t="n"/>
+      <c r="K191" s="7" t="n"/>
+      <c r="L191" s="7" t="n"/>
+      <c r="M191" s="7" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="n"/>
       <c r="F192" s="12" t="n"/>
-      <c r="G192" s="7" t="n"/>
-      <c r="H192" s="7" t="n"/>
-      <c r="I192" s="7" t="n"/>
+      <c r="J192" s="12" t="n"/>
+      <c r="K192" s="7" t="n"/>
+      <c r="L192" s="7" t="n"/>
+      <c r="M192" s="7" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="n"/>
       <c r="F193" s="12" t="n"/>
-      <c r="G193" s="7" t="n"/>
-      <c r="H193" s="7" t="n"/>
-      <c r="I193" s="7" t="n"/>
+      <c r="J193" s="12" t="n"/>
+      <c r="K193" s="7" t="n"/>
+      <c r="L193" s="7" t="n"/>
+      <c r="M193" s="7" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="n"/>
       <c r="F194" s="12" t="n"/>
-      <c r="G194" s="7" t="n"/>
-      <c r="H194" s="7" t="n"/>
-      <c r="I194" s="7" t="n"/>
+      <c r="J194" s="12" t="n"/>
+      <c r="K194" s="7" t="n"/>
+      <c r="L194" s="7" t="n"/>
+      <c r="M194" s="7" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="n"/>
       <c r="F195" s="12" t="n"/>
-      <c r="G195" s="7" t="n"/>
-      <c r="H195" s="7" t="n"/>
-      <c r="I195" s="7" t="n"/>
+      <c r="J195" s="12" t="n"/>
+      <c r="K195" s="7" t="n"/>
+      <c r="L195" s="7" t="n"/>
+      <c r="M195" s="7" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="n"/>
       <c r="F196" s="12" t="n"/>
-      <c r="G196" s="7" t="n"/>
-      <c r="H196" s="7" t="n"/>
-      <c r="I196" s="7" t="n"/>
+      <c r="J196" s="12" t="n"/>
+      <c r="K196" s="7" t="n"/>
+      <c r="L196" s="7" t="n"/>
+      <c r="M196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="n"/>
       <c r="F197" s="12" t="n"/>
-      <c r="G197" s="7" t="n"/>
-      <c r="H197" s="7" t="n"/>
-      <c r="I197" s="7" t="n"/>
+      <c r="J197" s="12" t="n"/>
+      <c r="K197" s="7" t="n"/>
+      <c r="L197" s="7" t="n"/>
+      <c r="M197" s="7" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="n"/>
       <c r="F198" s="12" t="n"/>
-      <c r="G198" s="7" t="n"/>
-      <c r="H198" s="7" t="n"/>
-      <c r="I198" s="7" t="n"/>
+      <c r="J198" s="12" t="n"/>
+      <c r="K198" s="7" t="n"/>
+      <c r="L198" s="7" t="n"/>
+      <c r="M198" s="7" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="n"/>
       <c r="F199" s="12" t="n"/>
-      <c r="G199" s="7" t="n"/>
-      <c r="H199" s="7" t="n"/>
-      <c r="I199" s="7" t="n"/>
+      <c r="J199" s="12" t="n"/>
+      <c r="K199" s="7" t="n"/>
+      <c r="L199" s="7" t="n"/>
+      <c r="M199" s="7" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="n"/>
       <c r="F200" s="12" t="n"/>
-      <c r="G200" s="7" t="n"/>
-      <c r="H200" s="7" t="n"/>
-      <c r="I200" s="7" t="n"/>
+      <c r="J200" s="12" t="n"/>
+      <c r="K200" s="7" t="n"/>
+      <c r="L200" s="7" t="n"/>
+      <c r="M200" s="7" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="n"/>
       <c r="F201" s="12" t="n"/>
-      <c r="G201" s="7" t="n"/>
-      <c r="H201" s="7" t="n"/>
-      <c r="I201" s="7" t="n"/>
+      <c r="J201" s="12" t="n"/>
+      <c r="K201" s="7" t="n"/>
+      <c r="L201" s="7" t="n"/>
+      <c r="M201" s="7" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="n"/>
       <c r="F202" s="12" t="n"/>
-      <c r="G202" s="7" t="n"/>
-      <c r="H202" s="7" t="n"/>
-      <c r="I202" s="7" t="n"/>
+      <c r="J202" s="12" t="n"/>
+      <c r="K202" s="7" t="n"/>
+      <c r="L202" s="7" t="n"/>
+      <c r="M202" s="7" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="n"/>
       <c r="F203" s="12" t="n"/>
-      <c r="G203" s="7" t="n"/>
-      <c r="H203" s="7" t="n"/>
-      <c r="I203" s="7" t="n"/>
+      <c r="J203" s="12" t="n"/>
+      <c r="K203" s="7" t="n"/>
+      <c r="L203" s="7" t="n"/>
+      <c r="M203" s="7" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="n"/>
       <c r="F204" s="12" t="n"/>
-      <c r="G204" s="7" t="n"/>
-      <c r="H204" s="7" t="n"/>
-      <c r="I204" s="7" t="n"/>
+      <c r="J204" s="12" t="n"/>
+      <c r="K204" s="7" t="n"/>
+      <c r="L204" s="7" t="n"/>
+      <c r="M204" s="7" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="n"/>
       <c r="F205" s="12" t="n"/>
-      <c r="G205" s="7" t="n"/>
-      <c r="H205" s="7" t="n"/>
-      <c r="I205" s="7" t="n"/>
+      <c r="J205" s="12" t="n"/>
+      <c r="K205" s="7" t="n"/>
+      <c r="L205" s="7" t="n"/>
+      <c r="M205" s="7" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="n"/>
       <c r="F206" s="12" t="n"/>
-      <c r="G206" s="7" t="n"/>
-      <c r="H206" s="7" t="n"/>
-      <c r="I206" s="7" t="n"/>
+      <c r="J206" s="12" t="n"/>
+      <c r="K206" s="7" t="n"/>
+      <c r="L206" s="7" t="n"/>
+      <c r="M206" s="7" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="n"/>
       <c r="F207" s="12" t="n"/>
-      <c r="G207" s="7" t="n"/>
-      <c r="H207" s="7" t="n"/>
-      <c r="I207" s="7" t="n"/>
+      <c r="J207" s="12" t="n"/>
+      <c r="K207" s="7" t="n"/>
+      <c r="L207" s="7" t="n"/>
+      <c r="M207" s="7" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="6" t="n"/>
       <c r="F208" s="12" t="n"/>
-      <c r="G208" s="7" t="n"/>
-      <c r="H208" s="7" t="n"/>
-      <c r="I208" s="7" t="n"/>
+      <c r="J208" s="12" t="n"/>
+      <c r="K208" s="7" t="n"/>
+      <c r="L208" s="7" t="n"/>
+      <c r="M208" s="7" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="6" t="n"/>
       <c r="F209" s="12" t="n"/>
-      <c r="G209" s="7" t="n"/>
-      <c r="H209" s="7" t="n"/>
-      <c r="I209" s="7" t="n"/>
+      <c r="J209" s="12" t="n"/>
+      <c r="K209" s="7" t="n"/>
+      <c r="L209" s="7" t="n"/>
+      <c r="M209" s="7" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="n"/>
       <c r="F210" s="12" t="n"/>
-      <c r="G210" s="7" t="n"/>
-      <c r="H210" s="7" t="n"/>
-      <c r="I210" s="7" t="n"/>
+      <c r="J210" s="12" t="n"/>
+      <c r="K210" s="7" t="n"/>
+      <c r="L210" s="7" t="n"/>
+      <c r="M210" s="7" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="n"/>
       <c r="F211" s="12" t="n"/>
-      <c r="G211" s="7" t="n"/>
-      <c r="H211" s="7" t="n"/>
-      <c r="I211" s="7" t="n"/>
+      <c r="J211" s="12" t="n"/>
+      <c r="K211" s="7" t="n"/>
+      <c r="L211" s="7" t="n"/>
+      <c r="M211" s="7" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="6" t="n"/>
       <c r="F212" s="12" t="n"/>
-      <c r="G212" s="7" t="n"/>
-      <c r="H212" s="7" t="n"/>
-      <c r="I212" s="7" t="n"/>
+      <c r="J212" s="12" t="n"/>
+      <c r="K212" s="7" t="n"/>
+      <c r="L212" s="7" t="n"/>
+      <c r="M212" s="7" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="n"/>
       <c r="F213" s="12" t="n"/>
-      <c r="G213" s="7" t="n"/>
-      <c r="H213" s="7" t="n"/>
-      <c r="I213" s="7" t="n"/>
+      <c r="J213" s="12" t="n"/>
+      <c r="K213" s="7" t="n"/>
+      <c r="L213" s="7" t="n"/>
+      <c r="M213" s="7" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="6" t="n"/>
       <c r="F214" s="12" t="n"/>
-      <c r="G214" s="7" t="n"/>
-      <c r="H214" s="7" t="n"/>
-      <c r="I214" s="7" t="n"/>
+      <c r="J214" s="12" t="n"/>
+      <c r="K214" s="7" t="n"/>
+      <c r="L214" s="7" t="n"/>
+      <c r="M214" s="7" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="n"/>
       <c r="F215" s="12" t="n"/>
-      <c r="G215" s="7" t="n"/>
-      <c r="H215" s="7" t="n"/>
-      <c r="I215" s="7" t="n"/>
+      <c r="J215" s="12" t="n"/>
+      <c r="K215" s="7" t="n"/>
+      <c r="L215" s="7" t="n"/>
+      <c r="M215" s="7" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="n"/>
       <c r="F216" s="12" t="n"/>
-      <c r="G216" s="7" t="n"/>
-      <c r="H216" s="7" t="n"/>
-      <c r="I216" s="7" t="n"/>
+      <c r="J216" s="12" t="n"/>
+      <c r="K216" s="7" t="n"/>
+      <c r="L216" s="7" t="n"/>
+      <c r="M216" s="7" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="n"/>
       <c r="F217" s="12" t="n"/>
-      <c r="G217" s="7" t="n"/>
-      <c r="H217" s="7" t="n"/>
-      <c r="I217" s="7" t="n"/>
+      <c r="J217" s="12" t="n"/>
+      <c r="K217" s="7" t="n"/>
+      <c r="L217" s="7" t="n"/>
+      <c r="M217" s="7" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="n"/>
       <c r="F218" s="12" t="n"/>
-      <c r="G218" s="7" t="n"/>
-      <c r="H218" s="7" t="n"/>
-      <c r="I218" s="7" t="n"/>
+      <c r="J218" s="12" t="n"/>
+      <c r="K218" s="7" t="n"/>
+      <c r="L218" s="7" t="n"/>
+      <c r="M218" s="7" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="n"/>
       <c r="F219" s="12" t="n"/>
-      <c r="G219" s="7" t="n"/>
-      <c r="H219" s="7" t="n"/>
-      <c r="I219" s="7" t="n"/>
+      <c r="J219" s="12" t="n"/>
+      <c r="K219" s="7" t="n"/>
+      <c r="L219" s="7" t="n"/>
+      <c r="M219" s="7" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="6" t="n"/>
       <c r="F220" s="12" t="n"/>
-      <c r="G220" s="7" t="n"/>
-      <c r="H220" s="7" t="n"/>
-      <c r="I220" s="7" t="n"/>
+      <c r="J220" s="12" t="n"/>
+      <c r="K220" s="7" t="n"/>
+      <c r="L220" s="7" t="n"/>
+      <c r="M220" s="7" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="n"/>
       <c r="F221" s="12" t="n"/>
-      <c r="G221" s="7" t="n"/>
-      <c r="H221" s="7" t="n"/>
-      <c r="I221" s="7" t="n"/>
+      <c r="J221" s="12" t="n"/>
+      <c r="K221" s="7" t="n"/>
+      <c r="L221" s="7" t="n"/>
+      <c r="M221" s="7" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="6" t="n"/>
       <c r="F222" s="12" t="n"/>
-      <c r="G222" s="7" t="n"/>
-      <c r="H222" s="7" t="n"/>
-      <c r="I222" s="7" t="n"/>
+      <c r="J222" s="12" t="n"/>
+      <c r="K222" s="7" t="n"/>
+      <c r="L222" s="7" t="n"/>
+      <c r="M222" s="7" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="n"/>
       <c r="F223" s="12" t="n"/>
-      <c r="G223" s="7" t="n"/>
-      <c r="H223" s="7" t="n"/>
-      <c r="I223" s="7" t="n"/>
+      <c r="J223" s="12" t="n"/>
+      <c r="K223" s="7" t="n"/>
+      <c r="L223" s="7" t="n"/>
+      <c r="M223" s="7" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="n"/>
       <c r="F224" s="12" t="n"/>
-      <c r="G224" s="7" t="n"/>
-      <c r="H224" s="7" t="n"/>
-      <c r="I224" s="7" t="n"/>
+      <c r="J224" s="12" t="n"/>
+      <c r="K224" s="7" t="n"/>
+      <c r="L224" s="7" t="n"/>
+      <c r="M224" s="7" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="n"/>
       <c r="F225" s="12" t="n"/>
-      <c r="G225" s="7" t="n"/>
-      <c r="H225" s="7" t="n"/>
-      <c r="I225" s="7" t="n"/>
+      <c r="J225" s="12" t="n"/>
+      <c r="K225" s="7" t="n"/>
+      <c r="L225" s="7" t="n"/>
+      <c r="M225" s="7" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="6" t="n"/>
       <c r="F226" s="12" t="n"/>
-      <c r="G226" s="7" t="n"/>
-      <c r="H226" s="7" t="n"/>
-      <c r="I226" s="7" t="n"/>
+      <c r="J226" s="12" t="n"/>
+      <c r="K226" s="7" t="n"/>
+      <c r="L226" s="7" t="n"/>
+      <c r="M226" s="7" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="n"/>
       <c r="F227" s="12" t="n"/>
-      <c r="G227" s="7" t="n"/>
-      <c r="H227" s="7" t="n"/>
-      <c r="I227" s="7" t="n"/>
+      <c r="J227" s="12" t="n"/>
+      <c r="K227" s="7" t="n"/>
+      <c r="L227" s="7" t="n"/>
+      <c r="M227" s="7" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="6" t="n"/>
       <c r="F228" s="12" t="n"/>
-      <c r="G228" s="7" t="n"/>
-      <c r="H228" s="7" t="n"/>
-      <c r="I228" s="7" t="n"/>
+      <c r="J228" s="12" t="n"/>
+      <c r="K228" s="7" t="n"/>
+      <c r="L228" s="7" t="n"/>
+      <c r="M228" s="7" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="6" t="n"/>
       <c r="F229" s="12" t="n"/>
-      <c r="G229" s="7" t="n"/>
-      <c r="H229" s="7" t="n"/>
-      <c r="I229" s="7" t="n"/>
+      <c r="J229" s="12" t="n"/>
+      <c r="K229" s="7" t="n"/>
+      <c r="L229" s="7" t="n"/>
+      <c r="M229" s="7" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="6" t="n"/>
       <c r="F230" s="12" t="n"/>
-      <c r="G230" s="7" t="n"/>
-      <c r="H230" s="7" t="n"/>
-      <c r="I230" s="7" t="n"/>
+      <c r="J230" s="12" t="n"/>
+      <c r="K230" s="7" t="n"/>
+      <c r="L230" s="7" t="n"/>
+      <c r="M230" s="7" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="n"/>
       <c r="F231" s="12" t="n"/>
-      <c r="G231" s="7" t="n"/>
-      <c r="H231" s="7" t="n"/>
-      <c r="I231" s="7" t="n"/>
+      <c r="J231" s="12" t="n"/>
+      <c r="K231" s="7" t="n"/>
+      <c r="L231" s="7" t="n"/>
+      <c r="M231" s="7" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="n"/>
       <c r="F232" s="12" t="n"/>
-      <c r="G232" s="7" t="n"/>
-      <c r="H232" s="7" t="n"/>
-      <c r="I232" s="7" t="n"/>
+      <c r="J232" s="12" t="n"/>
+      <c r="K232" s="7" t="n"/>
+      <c r="L232" s="7" t="n"/>
+      <c r="M232" s="7" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="n"/>
       <c r="F233" s="12" t="n"/>
-      <c r="G233" s="7" t="n"/>
-      <c r="H233" s="7" t="n"/>
-      <c r="I233" s="7" t="n"/>
+      <c r="J233" s="12" t="n"/>
+      <c r="K233" s="7" t="n"/>
+      <c r="L233" s="7" t="n"/>
+      <c r="M233" s="7" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="6" t="n"/>
       <c r="F234" s="12" t="n"/>
-      <c r="G234" s="7" t="n"/>
-      <c r="H234" s="7" t="n"/>
-      <c r="I234" s="7" t="n"/>
+      <c r="J234" s="12" t="n"/>
+      <c r="K234" s="7" t="n"/>
+      <c r="L234" s="7" t="n"/>
+      <c r="M234" s="7" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="6" t="n"/>
       <c r="F235" s="12" t="n"/>
-      <c r="G235" s="7" t="n"/>
-      <c r="H235" s="7" t="n"/>
-      <c r="I235" s="7" t="n"/>
+      <c r="J235" s="12" t="n"/>
+      <c r="K235" s="7" t="n"/>
+      <c r="L235" s="7" t="n"/>
+      <c r="M235" s="7" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="6" t="n"/>
       <c r="F236" s="12" t="n"/>
-      <c r="G236" s="7" t="n"/>
-      <c r="H236" s="7" t="n"/>
-      <c r="I236" s="7" t="n"/>
+      <c r="J236" s="12" t="n"/>
+      <c r="K236" s="7" t="n"/>
+      <c r="L236" s="7" t="n"/>
+      <c r="M236" s="7" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="n"/>
       <c r="F237" s="12" t="n"/>
-      <c r="G237" s="7" t="n"/>
-      <c r="H237" s="7" t="n"/>
-      <c r="I237" s="7" t="n"/>
+      <c r="J237" s="12" t="n"/>
+      <c r="K237" s="7" t="n"/>
+      <c r="L237" s="7" t="n"/>
+      <c r="M237" s="7" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="n"/>
       <c r="F238" s="12" t="n"/>
-      <c r="G238" s="7" t="n"/>
-      <c r="H238" s="7" t="n"/>
-      <c r="I238" s="7" t="n"/>
+      <c r="J238" s="12" t="n"/>
+      <c r="K238" s="7" t="n"/>
+      <c r="L238" s="7" t="n"/>
+      <c r="M238" s="7" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="n"/>
       <c r="F239" s="12" t="n"/>
-      <c r="G239" s="7" t="n"/>
-      <c r="H239" s="7" t="n"/>
-      <c r="I239" s="7" t="n"/>
+      <c r="J239" s="12" t="n"/>
+      <c r="K239" s="7" t="n"/>
+      <c r="L239" s="7" t="n"/>
+      <c r="M239" s="7" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="6" t="n"/>
       <c r="F240" s="12" t="n"/>
-      <c r="G240" s="7" t="n"/>
-      <c r="H240" s="7" t="n"/>
-      <c r="I240" s="7" t="n"/>
+      <c r="J240" s="12" t="n"/>
+      <c r="K240" s="7" t="n"/>
+      <c r="L240" s="7" t="n"/>
+      <c r="M240" s="7" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="n"/>
       <c r="F241" s="12" t="n"/>
-      <c r="G241" s="7" t="n"/>
-      <c r="H241" s="7" t="n"/>
-      <c r="I241" s="7" t="n"/>
+      <c r="J241" s="12" t="n"/>
+      <c r="K241" s="7" t="n"/>
+      <c r="L241" s="7" t="n"/>
+      <c r="M241" s="7" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="6" t="n"/>
       <c r="F242" s="12" t="n"/>
-      <c r="G242" s="7" t="n"/>
-      <c r="H242" s="7" t="n"/>
-      <c r="I242" s="7" t="n"/>
+      <c r="J242" s="12" t="n"/>
+      <c r="K242" s="7" t="n"/>
+      <c r="L242" s="7" t="n"/>
+      <c r="M242" s="7" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="6" t="n"/>
       <c r="F243" s="12" t="n"/>
-      <c r="G243" s="7" t="n"/>
-      <c r="H243" s="7" t="n"/>
-      <c r="I243" s="7" t="n"/>
+      <c r="J243" s="12" t="n"/>
+      <c r="K243" s="7" t="n"/>
+      <c r="L243" s="7" t="n"/>
+      <c r="M243" s="7" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="6" t="n"/>
       <c r="F244" s="12" t="n"/>
-      <c r="G244" s="7" t="n"/>
-      <c r="H244" s="7" t="n"/>
-      <c r="I244" s="7" t="n"/>
+      <c r="J244" s="12" t="n"/>
+      <c r="K244" s="7" t="n"/>
+      <c r="L244" s="7" t="n"/>
+      <c r="M244" s="7" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="n"/>
       <c r="F245" s="12" t="n"/>
-      <c r="G245" s="7" t="n"/>
-      <c r="H245" s="7" t="n"/>
-      <c r="I245" s="7" t="n"/>
+      <c r="J245" s="12" t="n"/>
+      <c r="K245" s="7" t="n"/>
+      <c r="L245" s="7" t="n"/>
+      <c r="M245" s="7" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="n"/>
       <c r="F246" s="12" t="n"/>
-      <c r="G246" s="7" t="n"/>
-      <c r="H246" s="7" t="n"/>
-      <c r="I246" s="7" t="n"/>
+      <c r="J246" s="12" t="n"/>
+      <c r="K246" s="7" t="n"/>
+      <c r="L246" s="7" t="n"/>
+      <c r="M246" s="7" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="n"/>
       <c r="F247" s="12" t="n"/>
-      <c r="G247" s="7" t="n"/>
-      <c r="H247" s="7" t="n"/>
-      <c r="I247" s="7" t="n"/>
+      <c r="J247" s="12" t="n"/>
+      <c r="K247" s="7" t="n"/>
+      <c r="L247" s="7" t="n"/>
+      <c r="M247" s="7" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="6" t="n"/>
       <c r="F248" s="12" t="n"/>
-      <c r="G248" s="7" t="n"/>
-      <c r="H248" s="7" t="n"/>
-      <c r="I248" s="7" t="n"/>
+      <c r="J248" s="12" t="n"/>
+      <c r="K248" s="7" t="n"/>
+      <c r="L248" s="7" t="n"/>
+      <c r="M248" s="7" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="n"/>
       <c r="F249" s="12" t="n"/>
-      <c r="G249" s="7" t="n"/>
-      <c r="H249" s="7" t="n"/>
-      <c r="I249" s="7" t="n"/>
+      <c r="J249" s="12" t="n"/>
+      <c r="K249" s="7" t="n"/>
+      <c r="L249" s="7" t="n"/>
+      <c r="M249" s="7" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="6" t="n"/>
       <c r="F250" s="12" t="n"/>
-      <c r="G250" s="7" t="n"/>
-      <c r="H250" s="7" t="n"/>
-      <c r="I250" s="7" t="n"/>
+      <c r="J250" s="12" t="n"/>
+      <c r="K250" s="7" t="n"/>
+      <c r="L250" s="7" t="n"/>
+      <c r="M250" s="7" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="n"/>
       <c r="F251" s="12" t="n"/>
-      <c r="G251" s="7" t="n"/>
-      <c r="H251" s="7" t="n"/>
-      <c r="I251" s="7" t="n"/>
+      <c r="J251" s="12" t="n"/>
+      <c r="K251" s="7" t="n"/>
+      <c r="L251" s="7" t="n"/>
+      <c r="M251" s="7" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="n"/>
       <c r="F252" s="12" t="n"/>
-      <c r="G252" s="7" t="n"/>
-      <c r="H252" s="7" t="n"/>
-      <c r="I252" s="7" t="n"/>
+      <c r="J252" s="12" t="n"/>
+      <c r="K252" s="7" t="n"/>
+      <c r="L252" s="7" t="n"/>
+      <c r="M252" s="7" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="n"/>
       <c r="F253" s="12" t="n"/>
-      <c r="G253" s="7" t="n"/>
-      <c r="H253" s="7" t="n"/>
-      <c r="I253" s="7" t="n"/>
+      <c r="J253" s="12" t="n"/>
+      <c r="K253" s="7" t="n"/>
+      <c r="L253" s="7" t="n"/>
+      <c r="M253" s="7" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="6" t="n"/>
       <c r="F254" s="12" t="n"/>
-      <c r="G254" s="7" t="n"/>
-      <c r="H254" s="7" t="n"/>
-      <c r="I254" s="7" t="n"/>
+      <c r="J254" s="12" t="n"/>
+      <c r="K254" s="7" t="n"/>
+      <c r="L254" s="7" t="n"/>
+      <c r="M254" s="7" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="n"/>
       <c r="F255" s="12" t="n"/>
-      <c r="G255" s="7" t="n"/>
-      <c r="H255" s="7" t="n"/>
-      <c r="I255" s="7" t="n"/>
+      <c r="J255" s="12" t="n"/>
+      <c r="K255" s="7" t="n"/>
+      <c r="L255" s="7" t="n"/>
+      <c r="M255" s="7" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="n"/>
       <c r="F256" s="12" t="n"/>
-      <c r="G256" s="7" t="n"/>
-      <c r="H256" s="7" t="n"/>
-      <c r="I256" s="7" t="n"/>
+      <c r="J256" s="12" t="n"/>
+      <c r="K256" s="7" t="n"/>
+      <c r="L256" s="7" t="n"/>
+      <c r="M256" s="7" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="n"/>
       <c r="F257" s="12" t="n"/>
-      <c r="G257" s="7" t="n"/>
-      <c r="H257" s="7" t="n"/>
-      <c r="I257" s="7" t="n"/>
+      <c r="J257" s="12" t="n"/>
+      <c r="K257" s="7" t="n"/>
+      <c r="L257" s="7" t="n"/>
+      <c r="M257" s="7" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="6" t="n"/>
       <c r="F258" s="12" t="n"/>
-      <c r="G258" s="7" t="n"/>
-      <c r="H258" s="7" t="n"/>
-      <c r="I258" s="7" t="n"/>
+      <c r="J258" s="12" t="n"/>
+      <c r="K258" s="7" t="n"/>
+      <c r="L258" s="7" t="n"/>
+      <c r="M258" s="7" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="n"/>
       <c r="F259" s="12" t="n"/>
-      <c r="G259" s="7" t="n"/>
-      <c r="H259" s="7" t="n"/>
-      <c r="I259" s="7" t="n"/>
+      <c r="J259" s="12" t="n"/>
+      <c r="K259" s="7" t="n"/>
+      <c r="L259" s="7" t="n"/>
+      <c r="M259" s="7" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="n"/>
       <c r="F260" s="12" t="n"/>
-      <c r="G260" s="7" t="n"/>
-      <c r="H260" s="7" t="n"/>
-      <c r="I260" s="7" t="n"/>
+      <c r="J260" s="12" t="n"/>
+      <c r="K260" s="7" t="n"/>
+      <c r="L260" s="7" t="n"/>
+      <c r="M260" s="7" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="6" t="n"/>
       <c r="F261" s="12" t="n"/>
-      <c r="G261" s="7" t="n"/>
-      <c r="H261" s="7" t="n"/>
-      <c r="I261" s="7" t="n"/>
+      <c r="J261" s="12" t="n"/>
+      <c r="K261" s="7" t="n"/>
+      <c r="L261" s="7" t="n"/>
+      <c r="M261" s="7" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="6" t="n"/>
       <c r="F262" s="12" t="n"/>
-      <c r="G262" s="7" t="n"/>
-      <c r="H262" s="7" t="n"/>
-      <c r="I262" s="7" t="n"/>
+      <c r="J262" s="12" t="n"/>
+      <c r="K262" s="7" t="n"/>
+      <c r="L262" s="7" t="n"/>
+      <c r="M262" s="7" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="6" t="n"/>
       <c r="F263" s="12" t="n"/>
-      <c r="G263" s="7" t="n"/>
-      <c r="H263" s="7" t="n"/>
-      <c r="I263" s="7" t="n"/>
+      <c r="J263" s="12" t="n"/>
+      <c r="K263" s="7" t="n"/>
+      <c r="L263" s="7" t="n"/>
+      <c r="M263" s="7" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="6" t="n"/>
       <c r="F264" s="12" t="n"/>
-      <c r="G264" s="7" t="n"/>
-      <c r="H264" s="7" t="n"/>
-      <c r="I264" s="7" t="n"/>
+      <c r="J264" s="12" t="n"/>
+      <c r="K264" s="7" t="n"/>
+      <c r="L264" s="7" t="n"/>
+      <c r="M264" s="7" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="6" t="n"/>
       <c r="F265" s="12" t="n"/>
-      <c r="G265" s="7" t="n"/>
-      <c r="H265" s="7" t="n"/>
-      <c r="I265" s="7" t="n"/>
+      <c r="J265" s="12" t="n"/>
+      <c r="K265" s="7" t="n"/>
+      <c r="L265" s="7" t="n"/>
+      <c r="M265" s="7" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="6" t="n"/>
       <c r="F266" s="12" t="n"/>
-      <c r="G266" s="7" t="n"/>
-      <c r="H266" s="7" t="n"/>
-      <c r="I266" s="7" t="n"/>
+      <c r="J266" s="12" t="n"/>
+      <c r="K266" s="7" t="n"/>
+      <c r="L266" s="7" t="n"/>
+      <c r="M266" s="7" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="6" t="n"/>
       <c r="F267" s="12" t="n"/>
-      <c r="G267" s="7" t="n"/>
-      <c r="H267" s="7" t="n"/>
-      <c r="I267" s="7" t="n"/>
+      <c r="J267" s="12" t="n"/>
+      <c r="K267" s="7" t="n"/>
+      <c r="L267" s="7" t="n"/>
+      <c r="M267" s="7" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="6" t="n"/>
       <c r="F268" s="12" t="n"/>
-      <c r="G268" s="7" t="n"/>
-      <c r="H268" s="7" t="n"/>
-      <c r="I268" s="7" t="n"/>
+      <c r="J268" s="12" t="n"/>
+      <c r="K268" s="7" t="n"/>
+      <c r="L268" s="7" t="n"/>
+      <c r="M268" s="7" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="6" t="n"/>
       <c r="F269" s="12" t="n"/>
-      <c r="G269" s="7" t="n"/>
-      <c r="H269" s="7" t="n"/>
-      <c r="I269" s="7" t="n"/>
+      <c r="J269" s="12" t="n"/>
+      <c r="K269" s="7" t="n"/>
+      <c r="L269" s="7" t="n"/>
+      <c r="M269" s="7" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="6" t="n"/>
       <c r="F270" s="12" t="n"/>
-      <c r="G270" s="7" t="n"/>
-      <c r="H270" s="7" t="n"/>
-      <c r="I270" s="7" t="n"/>
+      <c r="J270" s="12" t="n"/>
+      <c r="K270" s="7" t="n"/>
+      <c r="L270" s="7" t="n"/>
+      <c r="M270" s="7" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="6" t="n"/>
       <c r="F271" s="12" t="n"/>
-      <c r="G271" s="7" t="n"/>
-      <c r="H271" s="7" t="n"/>
-      <c r="I271" s="7" t="n"/>
+      <c r="J271" s="12" t="n"/>
+      <c r="K271" s="7" t="n"/>
+      <c r="L271" s="7" t="n"/>
+      <c r="M271" s="7" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="6" t="n"/>
       <c r="F272" s="12" t="n"/>
-      <c r="G272" s="7" t="n"/>
-      <c r="H272" s="7" t="n"/>
-      <c r="I272" s="7" t="n"/>
+      <c r="J272" s="12" t="n"/>
+      <c r="K272" s="7" t="n"/>
+      <c r="L272" s="7" t="n"/>
+      <c r="M272" s="7" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="6" t="n"/>
       <c r="F273" s="12" t="n"/>
-      <c r="G273" s="7" t="n"/>
-      <c r="H273" s="7" t="n"/>
-      <c r="I273" s="7" t="n"/>
+      <c r="J273" s="12" t="n"/>
+      <c r="K273" s="7" t="n"/>
+      <c r="L273" s="7" t="n"/>
+      <c r="M273" s="7" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="6" t="n"/>
       <c r="F274" s="12" t="n"/>
-      <c r="G274" s="7" t="n"/>
-      <c r="H274" s="7" t="n"/>
-      <c r="I274" s="7" t="n"/>
+      <c r="J274" s="12" t="n"/>
+      <c r="K274" s="7" t="n"/>
+      <c r="L274" s="7" t="n"/>
+      <c r="M274" s="7" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="6" t="n"/>
       <c r="F275" s="12" t="n"/>
-      <c r="G275" s="7" t="n"/>
-      <c r="H275" s="7" t="n"/>
-      <c r="I275" s="7" t="n"/>
+      <c r="J275" s="12" t="n"/>
+      <c r="K275" s="7" t="n"/>
+      <c r="L275" s="7" t="n"/>
+      <c r="M275" s="7" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="6" t="n"/>
       <c r="F276" s="12" t="n"/>
-      <c r="G276" s="7" t="n"/>
-      <c r="H276" s="7" t="n"/>
-      <c r="I276" s="7" t="n"/>
+      <c r="J276" s="12" t="n"/>
+      <c r="K276" s="7" t="n"/>
+      <c r="L276" s="7" t="n"/>
+      <c r="M276" s="7" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="6" t="n"/>
       <c r="F277" s="12" t="n"/>
-      <c r="G277" s="7" t="n"/>
-      <c r="H277" s="7" t="n"/>
-      <c r="I277" s="7" t="n"/>
+      <c r="J277" s="12" t="n"/>
+      <c r="K277" s="7" t="n"/>
+      <c r="L277" s="7" t="n"/>
+      <c r="M277" s="7" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="6" t="n"/>
       <c r="F278" s="12" t="n"/>
-      <c r="G278" s="7" t="n"/>
-      <c r="H278" s="7" t="n"/>
-      <c r="I278" s="7" t="n"/>
+      <c r="J278" s="12" t="n"/>
+      <c r="K278" s="7" t="n"/>
+      <c r="L278" s="7" t="n"/>
+      <c r="M278" s="7" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="n"/>
       <c r="F279" s="12" t="n"/>
-      <c r="G279" s="7" t="n"/>
-      <c r="H279" s="7" t="n"/>
-      <c r="I279" s="7" t="n"/>
+      <c r="J279" s="12" t="n"/>
+      <c r="K279" s="7" t="n"/>
+      <c r="L279" s="7" t="n"/>
+      <c r="M279" s="7" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="6" t="n"/>
       <c r="F280" s="12" t="n"/>
-      <c r="G280" s="7" t="n"/>
-      <c r="H280" s="7" t="n"/>
-      <c r="I280" s="7" t="n"/>
+      <c r="J280" s="12" t="n"/>
+      <c r="K280" s="7" t="n"/>
+      <c r="L280" s="7" t="n"/>
+      <c r="M280" s="7" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="6" t="n"/>
       <c r="F281" s="12" t="n"/>
-      <c r="G281" s="7" t="n"/>
-      <c r="H281" s="7" t="n"/>
-      <c r="I281" s="7" t="n"/>
+      <c r="J281" s="12" t="n"/>
+      <c r="K281" s="7" t="n"/>
+      <c r="L281" s="7" t="n"/>
+      <c r="M281" s="7" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="6" t="n"/>
       <c r="F282" s="12" t="n"/>
-      <c r="G282" s="7" t="n"/>
-      <c r="H282" s="7" t="n"/>
-      <c r="I282" s="7" t="n"/>
+      <c r="J282" s="12" t="n"/>
+      <c r="K282" s="7" t="n"/>
+      <c r="L282" s="7" t="n"/>
+      <c r="M282" s="7" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="6" t="n"/>
       <c r="F283" s="12" t="n"/>
-      <c r="G283" s="7" t="n"/>
-      <c r="H283" s="7" t="n"/>
-      <c r="I283" s="7" t="n"/>
+      <c r="J283" s="12" t="n"/>
+      <c r="K283" s="7" t="n"/>
+      <c r="L283" s="7" t="n"/>
+      <c r="M283" s="7" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="6" t="n"/>
       <c r="F284" s="12" t="n"/>
-      <c r="G284" s="7" t="n"/>
-      <c r="H284" s="7" t="n"/>
-      <c r="I284" s="7" t="n"/>
+      <c r="J284" s="12" t="n"/>
+      <c r="K284" s="7" t="n"/>
+      <c r="L284" s="7" t="n"/>
+      <c r="M284" s="7" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="6" t="n"/>
       <c r="F285" s="12" t="n"/>
-      <c r="G285" s="7" t="n"/>
-      <c r="H285" s="7" t="n"/>
-      <c r="I285" s="7" t="n"/>
+      <c r="J285" s="12" t="n"/>
+      <c r="K285" s="7" t="n"/>
+      <c r="L285" s="7" t="n"/>
+      <c r="M285" s="7" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="6" t="n"/>
       <c r="F286" s="12" t="n"/>
-      <c r="G286" s="7" t="n"/>
-      <c r="H286" s="7" t="n"/>
-      <c r="I286" s="7" t="n"/>
+      <c r="J286" s="12" t="n"/>
+      <c r="K286" s="7" t="n"/>
+      <c r="L286" s="7" t="n"/>
+      <c r="M286" s="7" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="6" t="n"/>
       <c r="F287" s="12" t="n"/>
-      <c r="G287" s="7" t="n"/>
-      <c r="H287" s="7" t="n"/>
-      <c r="I287" s="7" t="n"/>
+      <c r="J287" s="12" t="n"/>
+      <c r="K287" s="7" t="n"/>
+      <c r="L287" s="7" t="n"/>
+      <c r="M287" s="7" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="6" t="n"/>
       <c r="F288" s="12" t="n"/>
-      <c r="G288" s="7" t="n"/>
-      <c r="H288" s="7" t="n"/>
-      <c r="I288" s="7" t="n"/>
+      <c r="J288" s="12" t="n"/>
+      <c r="K288" s="7" t="n"/>
+      <c r="L288" s="7" t="n"/>
+      <c r="M288" s="7" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="6" t="n"/>
       <c r="F289" s="12" t="n"/>
-      <c r="G289" s="7" t="n"/>
-      <c r="H289" s="7" t="n"/>
-      <c r="I289" s="7" t="n"/>
+      <c r="J289" s="12" t="n"/>
+      <c r="K289" s="7" t="n"/>
+      <c r="L289" s="7" t="n"/>
+      <c r="M289" s="7" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="6" t="n"/>
       <c r="F290" s="12" t="n"/>
-      <c r="G290" s="7" t="n"/>
-      <c r="H290" s="7" t="n"/>
-      <c r="I290" s="7" t="n"/>
+      <c r="J290" s="12" t="n"/>
+      <c r="K290" s="7" t="n"/>
+      <c r="L290" s="7" t="n"/>
+      <c r="M290" s="7" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="6" t="n"/>
       <c r="F291" s="12" t="n"/>
-      <c r="G291" s="7" t="n"/>
-      <c r="H291" s="7" t="n"/>
-      <c r="I291" s="7" t="n"/>
+      <c r="J291" s="12" t="n"/>
+      <c r="K291" s="7" t="n"/>
+      <c r="L291" s="7" t="n"/>
+      <c r="M291" s="7" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="6" t="n"/>
       <c r="F292" s="12" t="n"/>
-      <c r="G292" s="7" t="n"/>
-      <c r="H292" s="7" t="n"/>
-      <c r="I292" s="7" t="n"/>
+      <c r="J292" s="12" t="n"/>
+      <c r="K292" s="7" t="n"/>
+      <c r="L292" s="7" t="n"/>
+      <c r="M292" s="7" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="6" t="n"/>
       <c r="F293" s="12" t="n"/>
-      <c r="G293" s="7" t="n"/>
-      <c r="H293" s="7" t="n"/>
-      <c r="I293" s="7" t="n"/>
+      <c r="J293" s="12" t="n"/>
+      <c r="K293" s="7" t="n"/>
+      <c r="L293" s="7" t="n"/>
+      <c r="M293" s="7" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="6" t="n"/>
       <c r="F294" s="12" t="n"/>
-      <c r="G294" s="7" t="n"/>
-      <c r="H294" s="7" t="n"/>
-      <c r="I294" s="7" t="n"/>
+      <c r="J294" s="12" t="n"/>
+      <c r="K294" s="7" t="n"/>
+      <c r="L294" s="7" t="n"/>
+      <c r="M294" s="7" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="6" t="n"/>
       <c r="F295" s="12" t="n"/>
-      <c r="G295" s="7" t="n"/>
-      <c r="H295" s="7" t="n"/>
-      <c r="I295" s="7" t="n"/>
+      <c r="J295" s="12" t="n"/>
+      <c r="K295" s="7" t="n"/>
+      <c r="L295" s="7" t="n"/>
+      <c r="M295" s="7" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="6" t="n"/>
       <c r="F296" s="12" t="n"/>
-      <c r="G296" s="7" t="n"/>
-      <c r="H296" s="7" t="n"/>
-      <c r="I296" s="7" t="n"/>
+      <c r="J296" s="12" t="n"/>
+      <c r="K296" s="7" t="n"/>
+      <c r="L296" s="7" t="n"/>
+      <c r="M296" s="7" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="6" t="n"/>
       <c r="F297" s="12" t="n"/>
-      <c r="G297" s="7" t="n"/>
-      <c r="H297" s="7" t="n"/>
-      <c r="I297" s="7" t="n"/>
+      <c r="J297" s="12" t="n"/>
+      <c r="K297" s="7" t="n"/>
+      <c r="L297" s="7" t="n"/>
+      <c r="M297" s="7" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="6" t="n"/>
       <c r="F298" s="12" t="n"/>
-      <c r="G298" s="7" t="n"/>
-      <c r="H298" s="7" t="n"/>
-      <c r="I298" s="7" t="n"/>
+      <c r="J298" s="12" t="n"/>
+      <c r="K298" s="7" t="n"/>
+      <c r="L298" s="7" t="n"/>
+      <c r="M298" s="7" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="6" t="n"/>
       <c r="F299" s="12" t="n"/>
-      <c r="G299" s="7" t="n"/>
-      <c r="H299" s="7" t="n"/>
-      <c r="I299" s="7" t="n"/>
+      <c r="J299" s="12" t="n"/>
+      <c r="K299" s="7" t="n"/>
+      <c r="L299" s="7" t="n"/>
+      <c r="M299" s="7" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="6" t="n"/>
       <c r="F300" s="12" t="n"/>
-      <c r="G300" s="7" t="n"/>
-      <c r="H300" s="7" t="n"/>
-      <c r="I300" s="7" t="n"/>
+      <c r="J300" s="12" t="n"/>
+      <c r="K300" s="7" t="n"/>
+      <c r="L300" s="7" t="n"/>
+      <c r="M300" s="7" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="6" t="n"/>
       <c r="F301" s="12" t="n"/>
-      <c r="G301" s="7" t="n"/>
-      <c r="H301" s="7" t="n"/>
-      <c r="I301" s="7" t="n"/>
+      <c r="J301" s="12" t="n"/>
+      <c r="K301" s="7" t="n"/>
+      <c r="L301" s="7" t="n"/>
+      <c r="M301" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9416,6 +9766,1703 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PLAN DE ORGANIZACIÓN DEL TIEMPO — semana a semana</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Se llena el lunes antes de las 8:30 a. m. y se comparte con coordinación: es el registro de la jornada (calidad y seguridad en el trabajo). 42 horas a la semana, en franjas concretas con lugar. Si la semana cambia, se corrige aquí el mismo día. Contacto con clientes solo de lunes a viernes de 7:00 a. m. a 7:00 p. m. y sábados de 8:00 a. m. a 3:00 p. m.; nunca domingos ni festivos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Semana 1 · del</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Enviado a coordinación:</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Mañana de</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Qué (empresas, reuniones, citas, oficina)</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Tarde de</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Qué</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Observaciones / cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="17">
+        <f>(IF(AND(B6&lt;&gt;"",C6&lt;&gt;""),C6-B6,0)+IF(AND(F6&lt;&gt;"",G6&lt;&gt;""),G6-F6,0))*24</f>
+        <v/>
+      </c>
+      <c r="K6" s="16" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="17">
+        <f>(IF(AND(B7&lt;&gt;"",C7&lt;&gt;""),C7-B7,0)+IF(AND(F7&lt;&gt;"",G7&lt;&gt;""),G7-F7,0))*24</f>
+        <v/>
+      </c>
+      <c r="K7" s="16" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="17">
+        <f>(IF(AND(B8&lt;&gt;"",C8&lt;&gt;""),C8-B8,0)+IF(AND(F8&lt;&gt;"",G8&lt;&gt;""),G8-F8,0))*24</f>
+        <v/>
+      </c>
+      <c r="K8" s="16" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="17">
+        <f>(IF(AND(B9&lt;&gt;"",C9&lt;&gt;""),C9-B9,0)+IF(AND(F9&lt;&gt;"",G9&lt;&gt;""),G9-F9,0))*24</f>
+        <v/>
+      </c>
+      <c r="K9" s="16" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="17">
+        <f>(IF(AND(B10&lt;&gt;"",C10&lt;&gt;""),C10-B10,0)+IF(AND(F10&lt;&gt;"",G10&lt;&gt;""),G10-F10,0))*24</f>
+        <v/>
+      </c>
+      <c r="K10" s="16" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="17">
+        <f>(IF(AND(B11&lt;&gt;"",C11&lt;&gt;""),C11-B11,0)+IF(AND(F11&lt;&gt;"",G11&lt;&gt;""),G11-F11,0))*24</f>
+        <v/>
+      </c>
+      <c r="K11" s="16" t="n"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Total de la semana</t>
+        </is>
+      </c>
+      <c r="J12" s="18">
+        <f>SUM(J6:J11)</f>
+        <v/>
+      </c>
+      <c r="K12" s="4">
+        <f>IF(J12=0,"",IF(J12&lt;42,"Faltan "&amp;TEXT(42-J12,"0.0")&amp;" horas para las 42",IF(J12&gt;42,"Pasa de 42: ajustar","Cumple 42 horas")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Semana 2 · del</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Enviado a coordinación:</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Mañana de</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Qué (empresas, reuniones, citas, oficina)</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Tarde de</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Qué</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Observaciones / cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="17">
+        <f>(IF(AND(B16&lt;&gt;"",C16&lt;&gt;""),C16-B16,0)+IF(AND(F16&lt;&gt;"",G16&lt;&gt;""),G16-F16,0))*24</f>
+        <v/>
+      </c>
+      <c r="K16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="17">
+        <f>(IF(AND(B17&lt;&gt;"",C17&lt;&gt;""),C17-B17,0)+IF(AND(F17&lt;&gt;"",G17&lt;&gt;""),G17-F17,0))*24</f>
+        <v/>
+      </c>
+      <c r="K17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="17">
+        <f>(IF(AND(B18&lt;&gt;"",C18&lt;&gt;""),C18-B18,0)+IF(AND(F18&lt;&gt;"",G18&lt;&gt;""),G18-F18,0))*24</f>
+        <v/>
+      </c>
+      <c r="K18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="17">
+        <f>(IF(AND(B19&lt;&gt;"",C19&lt;&gt;""),C19-B19,0)+IF(AND(F19&lt;&gt;"",G19&lt;&gt;""),G19-F19,0))*24</f>
+        <v/>
+      </c>
+      <c r="K19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="17">
+        <f>(IF(AND(B20&lt;&gt;"",C20&lt;&gt;""),C20-B20,0)+IF(AND(F20&lt;&gt;"",G20&lt;&gt;""),G20-F20,0))*24</f>
+        <v/>
+      </c>
+      <c r="K20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="17">
+        <f>(IF(AND(B21&lt;&gt;"",C21&lt;&gt;""),C21-B21,0)+IF(AND(F21&lt;&gt;"",G21&lt;&gt;""),G21-F21,0))*24</f>
+        <v/>
+      </c>
+      <c r="K21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Total de la semana</t>
+        </is>
+      </c>
+      <c r="J22" s="18">
+        <f>SUM(J16:J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="4">
+        <f>IF(J22=0,"",IF(J22&lt;42,"Faltan "&amp;TEXT(42-J22,"0.0")&amp;" horas para las 42",IF(J22&gt;42,"Pasa de 42: ajustar","Cumple 42 horas")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Semana 3 · del</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Enviado a coordinación:</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Mañana de</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Qué (empresas, reuniones, citas, oficina)</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Tarde de</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Qué</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Observaciones / cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="16" t="n"/>
+      <c r="J26" s="17">
+        <f>(IF(AND(B26&lt;&gt;"",C26&lt;&gt;""),C26-B26,0)+IF(AND(F26&lt;&gt;"",G26&lt;&gt;""),G26-F26,0))*24</f>
+        <v/>
+      </c>
+      <c r="K26" s="16" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="17">
+        <f>(IF(AND(B27&lt;&gt;"",C27&lt;&gt;""),C27-B27,0)+IF(AND(F27&lt;&gt;"",G27&lt;&gt;""),G27-F27,0))*24</f>
+        <v/>
+      </c>
+      <c r="K27" s="16" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="17">
+        <f>(IF(AND(B28&lt;&gt;"",C28&lt;&gt;""),C28-B28,0)+IF(AND(F28&lt;&gt;"",G28&lt;&gt;""),G28-F28,0))*24</f>
+        <v/>
+      </c>
+      <c r="K28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="16" t="n"/>
+      <c r="J29" s="17">
+        <f>(IF(AND(B29&lt;&gt;"",C29&lt;&gt;""),C29-B29,0)+IF(AND(F29&lt;&gt;"",G29&lt;&gt;""),G29-F29,0))*24</f>
+        <v/>
+      </c>
+      <c r="K29" s="16" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="16" t="n"/>
+      <c r="J30" s="17">
+        <f>(IF(AND(B30&lt;&gt;"",C30&lt;&gt;""),C30-B30,0)+IF(AND(F30&lt;&gt;"",G30&lt;&gt;""),G30-F30,0))*24</f>
+        <v/>
+      </c>
+      <c r="K30" s="16" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="16" t="n"/>
+      <c r="J31" s="17">
+        <f>(IF(AND(B31&lt;&gt;"",C31&lt;&gt;""),C31-B31,0)+IF(AND(F31&lt;&gt;"",G31&lt;&gt;""),G31-F31,0))*24</f>
+        <v/>
+      </c>
+      <c r="K31" s="16" t="n"/>
+    </row>
+    <row r="32">
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Total de la semana</t>
+        </is>
+      </c>
+      <c r="J32" s="18">
+        <f>SUM(J26:J31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="4">
+        <f>IF(J32=0,"",IF(J32&lt;42,"Faltan "&amp;TEXT(42-J32,"0.0")&amp;" horas para las 42",IF(J32&gt;42,"Pasa de 42: ajustar","Cumple 42 horas")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Semana 4 · del</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Enviado a coordinación:</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="n"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Mañana de</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>Qué (empresas, reuniones, citas, oficina)</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Tarde de</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Qué</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>Observaciones / cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="16" t="n"/>
+      <c r="J36" s="17">
+        <f>(IF(AND(B36&lt;&gt;"",C36&lt;&gt;""),C36-B36,0)+IF(AND(F36&lt;&gt;"",G36&lt;&gt;""),G36-F36,0))*24</f>
+        <v/>
+      </c>
+      <c r="K36" s="16" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="16" t="n"/>
+      <c r="J37" s="17">
+        <f>(IF(AND(B37&lt;&gt;"",C37&lt;&gt;""),C37-B37,0)+IF(AND(F37&lt;&gt;"",G37&lt;&gt;""),G37-F37,0))*24</f>
+        <v/>
+      </c>
+      <c r="K37" s="16" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="16" t="n"/>
+      <c r="J38" s="17">
+        <f>(IF(AND(B38&lt;&gt;"",C38&lt;&gt;""),C38-B38,0)+IF(AND(F38&lt;&gt;"",G38&lt;&gt;""),G38-F38,0))*24</f>
+        <v/>
+      </c>
+      <c r="K38" s="16" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="16" t="n"/>
+      <c r="J39" s="17">
+        <f>(IF(AND(B39&lt;&gt;"",C39&lt;&gt;""),C39-B39,0)+IF(AND(F39&lt;&gt;"",G39&lt;&gt;""),G39-F39,0))*24</f>
+        <v/>
+      </c>
+      <c r="K39" s="16" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="16" t="n"/>
+      <c r="J40" s="17">
+        <f>(IF(AND(B40&lt;&gt;"",C40&lt;&gt;""),C40-B40,0)+IF(AND(F40&lt;&gt;"",G40&lt;&gt;""),G40-F40,0))*24</f>
+        <v/>
+      </c>
+      <c r="K40" s="16" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="16" t="n"/>
+      <c r="J41" s="17">
+        <f>(IF(AND(B41&lt;&gt;"",C41&lt;&gt;""),C41-B41,0)+IF(AND(F41&lt;&gt;"",G41&lt;&gt;""),G41-F41,0))*24</f>
+        <v/>
+      </c>
+      <c r="K41" s="16" t="n"/>
+    </row>
+    <row r="42">
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Total de la semana</t>
+        </is>
+      </c>
+      <c r="J42" s="18">
+        <f>SUM(J36:J41)</f>
+        <v/>
+      </c>
+      <c r="K42" s="4">
+        <f>IF(J42=0,"",IF(J42&lt;42,"Faltan "&amp;TEXT(42-J42,"0.0")&amp;" horas para las 42",IF(J42&gt;42,"Pasa de 42: ajustar","Cumple 42 horas")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Semana 5 · del</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Enviado a coordinación:</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Mañana de</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>Qué (empresas, reuniones, citas, oficina)</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Tarde de</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>Qué</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>Observaciones / cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="n"/>
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="16" t="n"/>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="16" t="n"/>
+      <c r="J46" s="17">
+        <f>(IF(AND(B46&lt;&gt;"",C46&lt;&gt;""),C46-B46,0)+IF(AND(F46&lt;&gt;"",G46&lt;&gt;""),G46-F46,0))*24</f>
+        <v/>
+      </c>
+      <c r="K46" s="16" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n"/>
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="15" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="16" t="n"/>
+      <c r="J47" s="17">
+        <f>(IF(AND(B47&lt;&gt;"",C47&lt;&gt;""),C47-B47,0)+IF(AND(F47&lt;&gt;"",G47&lt;&gt;""),G47-F47,0))*24</f>
+        <v/>
+      </c>
+      <c r="K47" s="16" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="n"/>
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="16" t="n"/>
+      <c r="F48" s="15" t="n"/>
+      <c r="G48" s="15" t="n"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="16" t="n"/>
+      <c r="J48" s="17">
+        <f>(IF(AND(B48&lt;&gt;"",C48&lt;&gt;""),C48-B48,0)+IF(AND(F48&lt;&gt;"",G48&lt;&gt;""),G48-F48,0))*24</f>
+        <v/>
+      </c>
+      <c r="K48" s="16" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="n"/>
+      <c r="C49" s="15" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="16" t="n"/>
+      <c r="F49" s="15" t="n"/>
+      <c r="G49" s="15" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="16" t="n"/>
+      <c r="J49" s="17">
+        <f>(IF(AND(B49&lt;&gt;"",C49&lt;&gt;""),C49-B49,0)+IF(AND(F49&lt;&gt;"",G49&lt;&gt;""),G49-F49,0))*24</f>
+        <v/>
+      </c>
+      <c r="K49" s="16" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="n"/>
+      <c r="C50" s="15" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="16" t="n"/>
+      <c r="F50" s="15" t="n"/>
+      <c r="G50" s="15" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="16" t="n"/>
+      <c r="J50" s="17">
+        <f>(IF(AND(B50&lt;&gt;"",C50&lt;&gt;""),C50-B50,0)+IF(AND(F50&lt;&gt;"",G50&lt;&gt;""),G50-F50,0))*24</f>
+        <v/>
+      </c>
+      <c r="K50" s="16" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="16" t="n"/>
+      <c r="F51" s="15" t="n"/>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="16" t="n"/>
+      <c r="J51" s="17">
+        <f>(IF(AND(B51&lt;&gt;"",C51&lt;&gt;""),C51-B51,0)+IF(AND(F51&lt;&gt;"",G51&lt;&gt;""),G51-F51,0))*24</f>
+        <v/>
+      </c>
+      <c r="K51" s="16" t="n"/>
+    </row>
+    <row r="52">
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Total de la semana</t>
+        </is>
+      </c>
+      <c r="J52" s="18">
+        <f>SUM(J46:J51)</f>
+        <v/>
+      </c>
+      <c r="K52" s="4">
+        <f>IF(J52=0,"",IF(J52&lt;42,"Faltan "&amp;TEXT(42-J52,"0.0")&amp;" horas para las 42",IF(J52&gt;42,"Pasa de 42: ajustar","Cumple 42 horas")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Semana 6 · del</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Enviado a coordinación:</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="n"/>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Mañana de</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>Qué (empresas, reuniones, citas, oficina)</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Tarde de</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>Qué</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>Observaciones / cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n"/>
+      <c r="C56" s="15" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="15" t="n"/>
+      <c r="G56" s="15" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="16" t="n"/>
+      <c r="J56" s="17">
+        <f>(IF(AND(B56&lt;&gt;"",C56&lt;&gt;""),C56-B56,0)+IF(AND(F56&lt;&gt;"",G56&lt;&gt;""),G56-F56,0))*24</f>
+        <v/>
+      </c>
+      <c r="K56" s="16" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="n"/>
+      <c r="C57" s="15" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="16" t="n"/>
+      <c r="F57" s="15" t="n"/>
+      <c r="G57" s="15" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="16" t="n"/>
+      <c r="J57" s="17">
+        <f>(IF(AND(B57&lt;&gt;"",C57&lt;&gt;""),C57-B57,0)+IF(AND(F57&lt;&gt;"",G57&lt;&gt;""),G57-F57,0))*24</f>
+        <v/>
+      </c>
+      <c r="K57" s="16" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="n"/>
+      <c r="C58" s="15" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="16" t="n"/>
+      <c r="F58" s="15" t="n"/>
+      <c r="G58" s="15" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="16" t="n"/>
+      <c r="J58" s="17">
+        <f>(IF(AND(B58&lt;&gt;"",C58&lt;&gt;""),C58-B58,0)+IF(AND(F58&lt;&gt;"",G58&lt;&gt;""),G58-F58,0))*24</f>
+        <v/>
+      </c>
+      <c r="K58" s="16" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="n"/>
+      <c r="C59" s="15" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="16" t="n"/>
+      <c r="F59" s="15" t="n"/>
+      <c r="G59" s="15" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="16" t="n"/>
+      <c r="J59" s="17">
+        <f>(IF(AND(B59&lt;&gt;"",C59&lt;&gt;""),C59-B59,0)+IF(AND(F59&lt;&gt;"",G59&lt;&gt;""),G59-F59,0))*24</f>
+        <v/>
+      </c>
+      <c r="K59" s="16" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="n"/>
+      <c r="C60" s="15" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="16" t="n"/>
+      <c r="F60" s="15" t="n"/>
+      <c r="G60" s="15" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="16" t="n"/>
+      <c r="J60" s="17">
+        <f>(IF(AND(B60&lt;&gt;"",C60&lt;&gt;""),C60-B60,0)+IF(AND(F60&lt;&gt;"",G60&lt;&gt;""),G60-F60,0))*24</f>
+        <v/>
+      </c>
+      <c r="K60" s="16" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="n"/>
+      <c r="C61" s="15" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="16" t="n"/>
+      <c r="F61" s="15" t="n"/>
+      <c r="G61" s="15" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="16" t="n"/>
+      <c r="J61" s="17">
+        <f>(IF(AND(B61&lt;&gt;"",C61&lt;&gt;""),C61-B61,0)+IF(AND(F61&lt;&gt;"",G61&lt;&gt;""),G61-F61,0))*24</f>
+        <v/>
+      </c>
+      <c r="K61" s="16" t="n"/>
+    </row>
+    <row r="62">
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Total de la semana</t>
+        </is>
+      </c>
+      <c r="J62" s="18">
+        <f>SUM(J56:J61)</f>
+        <v/>
+      </c>
+      <c r="K62" s="4">
+        <f>IF(J62=0,"",IF(J62&lt;42,"Faltan "&amp;TEXT(42-J62,"0.0")&amp;" horas para las 42",IF(J62&gt;42,"Pasa de 42: ajustar","Cumple 42 horas")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Semana 7 · del</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Enviado a coordinación:</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="n"/>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Mañana de</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>Qué (empresas, reuniones, citas, oficina)</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Tarde de</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>Qué</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>Observaciones / cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="n"/>
+      <c r="C66" s="15" t="n"/>
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="16" t="n"/>
+      <c r="F66" s="15" t="n"/>
+      <c r="G66" s="15" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="16" t="n"/>
+      <c r="J66" s="17">
+        <f>(IF(AND(B66&lt;&gt;"",C66&lt;&gt;""),C66-B66,0)+IF(AND(F66&lt;&gt;"",G66&lt;&gt;""),G66-F66,0))*24</f>
+        <v/>
+      </c>
+      <c r="K66" s="16" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="n"/>
+      <c r="C67" s="15" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="16" t="n"/>
+      <c r="F67" s="15" t="n"/>
+      <c r="G67" s="15" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="16" t="n"/>
+      <c r="J67" s="17">
+        <f>(IF(AND(B67&lt;&gt;"",C67&lt;&gt;""),C67-B67,0)+IF(AND(F67&lt;&gt;"",G67&lt;&gt;""),G67-F67,0))*24</f>
+        <v/>
+      </c>
+      <c r="K67" s="16" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="n"/>
+      <c r="C68" s="15" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="16" t="n"/>
+      <c r="F68" s="15" t="n"/>
+      <c r="G68" s="15" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="16" t="n"/>
+      <c r="J68" s="17">
+        <f>(IF(AND(B68&lt;&gt;"",C68&lt;&gt;""),C68-B68,0)+IF(AND(F68&lt;&gt;"",G68&lt;&gt;""),G68-F68,0))*24</f>
+        <v/>
+      </c>
+      <c r="K68" s="16" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="15" t="n"/>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="16" t="n"/>
+      <c r="F69" s="15" t="n"/>
+      <c r="G69" s="15" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="16" t="n"/>
+      <c r="J69" s="17">
+        <f>(IF(AND(B69&lt;&gt;"",C69&lt;&gt;""),C69-B69,0)+IF(AND(F69&lt;&gt;"",G69&lt;&gt;""),G69-F69,0))*24</f>
+        <v/>
+      </c>
+      <c r="K69" s="16" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="n"/>
+      <c r="C70" s="15" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="16" t="n"/>
+      <c r="F70" s="15" t="n"/>
+      <c r="G70" s="15" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="16" t="n"/>
+      <c r="J70" s="17">
+        <f>(IF(AND(B70&lt;&gt;"",C70&lt;&gt;""),C70-B70,0)+IF(AND(F70&lt;&gt;"",G70&lt;&gt;""),G70-F70,0))*24</f>
+        <v/>
+      </c>
+      <c r="K70" s="16" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="n"/>
+      <c r="C71" s="15" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="16" t="n"/>
+      <c r="F71" s="15" t="n"/>
+      <c r="G71" s="15" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="16" t="n"/>
+      <c r="J71" s="17">
+        <f>(IF(AND(B71&lt;&gt;"",C71&lt;&gt;""),C71-B71,0)+IF(AND(F71&lt;&gt;"",G71&lt;&gt;""),G71-F71,0))*24</f>
+        <v/>
+      </c>
+      <c r="K71" s="16" t="n"/>
+    </row>
+    <row r="72">
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Total de la semana</t>
+        </is>
+      </c>
+      <c r="J72" s="18">
+        <f>SUM(J66:J71)</f>
+        <v/>
+      </c>
+      <c r="K72" s="4">
+        <f>IF(J72=0,"",IF(J72&lt;42,"Faltan "&amp;TEXT(42-J72,"0.0")&amp;" horas para las 42",IF(J72&gt;42,"Pasa de 42: ajustar","Cumple 42 horas")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Semana 8 · del</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Enviado a coordinación:</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="n"/>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>Mañana de</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>Qué (empresas, reuniones, citas, oficina)</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Tarde de</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>Qué</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>Observaciones / cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="n"/>
+      <c r="C76" s="15" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="16" t="n"/>
+      <c r="F76" s="15" t="n"/>
+      <c r="G76" s="15" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="16" t="n"/>
+      <c r="J76" s="17">
+        <f>(IF(AND(B76&lt;&gt;"",C76&lt;&gt;""),C76-B76,0)+IF(AND(F76&lt;&gt;"",G76&lt;&gt;""),G76-F76,0))*24</f>
+        <v/>
+      </c>
+      <c r="K76" s="16" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="n"/>
+      <c r="C77" s="15" t="n"/>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="16" t="n"/>
+      <c r="F77" s="15" t="n"/>
+      <c r="G77" s="15" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="16" t="n"/>
+      <c r="J77" s="17">
+        <f>(IF(AND(B77&lt;&gt;"",C77&lt;&gt;""),C77-B77,0)+IF(AND(F77&lt;&gt;"",G77&lt;&gt;""),G77-F77,0))*24</f>
+        <v/>
+      </c>
+      <c r="K77" s="16" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="n"/>
+      <c r="C78" s="15" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="16" t="n"/>
+      <c r="F78" s="15" t="n"/>
+      <c r="G78" s="15" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="16" t="n"/>
+      <c r="J78" s="17">
+        <f>(IF(AND(B78&lt;&gt;"",C78&lt;&gt;""),C78-B78,0)+IF(AND(F78&lt;&gt;"",G78&lt;&gt;""),G78-F78,0))*24</f>
+        <v/>
+      </c>
+      <c r="K78" s="16" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="n"/>
+      <c r="C79" s="15" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="16" t="n"/>
+      <c r="F79" s="15" t="n"/>
+      <c r="G79" s="15" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="16" t="n"/>
+      <c r="J79" s="17">
+        <f>(IF(AND(B79&lt;&gt;"",C79&lt;&gt;""),C79-B79,0)+IF(AND(F79&lt;&gt;"",G79&lt;&gt;""),G79-F79,0))*24</f>
+        <v/>
+      </c>
+      <c r="K79" s="16" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="n"/>
+      <c r="C80" s="15" t="n"/>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="16" t="n"/>
+      <c r="F80" s="15" t="n"/>
+      <c r="G80" s="15" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="16" t="n"/>
+      <c r="J80" s="17">
+        <f>(IF(AND(B80&lt;&gt;"",C80&lt;&gt;""),C80-B80,0)+IF(AND(F80&lt;&gt;"",G80&lt;&gt;""),G80-F80,0))*24</f>
+        <v/>
+      </c>
+      <c r="K80" s="16" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="n"/>
+      <c r="C81" s="15" t="n"/>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="16" t="n"/>
+      <c r="F81" s="15" t="n"/>
+      <c r="G81" s="15" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="16" t="n"/>
+      <c r="J81" s="17">
+        <f>(IF(AND(B81&lt;&gt;"",C81&lt;&gt;""),C81-B81,0)+IF(AND(F81&lt;&gt;"",G81&lt;&gt;""),G81-F81,0))*24</f>
+        <v/>
+      </c>
+      <c r="K81" s="16" t="n"/>
+    </row>
+    <row r="82">
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Total de la semana</t>
+        </is>
+      </c>
+      <c r="J82" s="18">
+        <f>SUM(J76:J81)</f>
+        <v/>
+      </c>
+      <c r="K82" s="4">
+        <f>IF(J82=0,"",IF(J82&lt;42,"Faltan "&amp;TEXT(42-J82,"0.0")&amp;" horas para las 42",IF(J82&gt;42,"Pasa de 42: ajustar","Cumple 42 horas")))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:K2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D6 D7 D8 D9 D10 D11 D16 D17 D18 D19 D20 D21 D26 D27 D28 D29 D30 D31 D36 D37 D38 D39 D40 D41 D46 D47 D48 D49 D50 D51 D56 D57 D58 D59 D60 D61 D66 D67 D68 D69 D70 D71 D76 D77 D78 D79 D80 D81 H6 H7 H8 H9 H10 H11 H16 H17 H18 H19 H20 H21 H26 H27 H28 H29 H30 H31 H36 H37 H38 H39 H40 H41 H46 H47 H48 H49 H50 H51 H56 H57 H58 H59 H60 H61 H66 H67 H68 H69 H70 H71 H76 H77 H78 H79 H80 H81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sede,Casa,Calle / empresa,Virtual"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9827,7 +11874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9860,7 +11907,7 @@
           <t>Mes liquidado (primer día)</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n"/>
+      <c r="B2" s="19" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -9868,7 +11915,7 @@
           <t>Básico del mes (SMMLV + auxilio vigente)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="20" t="n">
         <v>2000000</v>
       </c>
     </row>
@@ -9925,7 +11972,7 @@
           <t>Soporte (recibo / factura)</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
@@ -14775,7 +16822,7 @@
           <t>TOTAL A PAGAR (antes de deducciones de ley)</t>
         </is>
       </c>
-      <c r="G312" s="16">
+      <c r="G312" s="22">
         <f>G309+G310+G311</f>
         <v/>
       </c>
@@ -14793,7 +16840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
